--- a/wiring/MESAC_Wiring_Crosswalk.xlsx
+++ b/wiring/MESAC_Wiring_Crosswalk.xlsx
@@ -556,12 +556,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">probe-in</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROPOSED</t>
+          <t xml:space="preserve">RESERVED</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continuity-trace the installed Renishaw MP-3 interface to CN200-3 and verify voltage, idle polarity, and fail-open behavior; MMS SKIP alone does not prove this is the retained probe conductor.</t>
+          <t xml:space="preserve">RESERVED 2026-08-21 (owner decision): probe out of scope per mesa/current_pin_authority.csv PROBE_SKIP1; hal_net none, TB3 IN15 spare. If re-scoped: continuity-trace the installed Renishaw MP-3 interface to CN200-3 and verify voltage, idle polarity, and fail-open behavior; MMS SKIP alone does not prove this is the retained probe conductor.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mandatory for magazine indexing (rungs 3401/33xx). Writer added in field_7i84u.hal:79 (net mag-in-pos &lt;= input-28) on 2026-08-06. Verify prox type/polarity before commissioning. | [RECON 2026-08-08 CONFIRMED: MAG_IN_POS = PRS-13 MIPRS 'MAGAZINE INPOSITION' wire 213 X0D, Dwg 4143075409 pg135. In-position strobe; tool-# bits are PRS-21..25 (711P/712P/714P/718P/721P). Supersedes prior 'PRS-13=tool bit'.] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE POSITION OK, wire 225, CN2-9/CND2-9 (trusted). pg135 read the in-position prox as PRS-13/wire 213, but wire 213 is absent from the BBIA-1 pinout; POSITION OK is 225/CN2-9. PLC-side prox remains PRS-13/X00D.] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
+          <t xml:space="preserve">Mandatory for magazine indexing (rungs 3401/33xx). Writer added in field_7i84u.hal (net mag-in-pos &lt;= input-28) on 2026-08-06. Verify prox type/polarity before commissioning. | [RECON 2026-08-08 CONFIRMED: MAG_IN_POS = PRS-13 MIPRS 'MAGAZINE INPOSITION' wire 213 X0D, Dwg 4143075409 pg135. In-position strobe; tool-# bits are PRS-21..25 (711P/712P/714P/718P/721P). Supersedes prior 'PRS-13=tool bit'.] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE POSITION OK, wire 225, CN2-9/CND2-9 (trusted). pg135 read the in-position prox as PRS-13/wire 213, but wire 213 appears in the BBIA-1 pinout only as the CN11-5 GEAR SHIFT LOW output, not on the CN2 input bank; POSITION OK is 225/CN2-9. PLC-side prox remains PRS-13/X00D.] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add HAL net when confirmed | [RECON 2026-08-08 §F: PHS-181 line 381 (settles PHS-127 vs 181) confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
+          <t xml:space="preserve">HAL net bound in atc_orient.hal | [RECON 2026-08-08 §F: PHS-181 line 381 (settles PHS-127 vs 181) confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Update field_7i84u.hal because it currently uses input-01 | [RECON 2026-08-08 §F: PRS-8 line 208 TUCPRS confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
+          <t xml:space="preserve">RESOLVED - field_7i84u.hal binds tool-unclamped to input-16 | [RECON 2026-08-08 §F: PRS-8 line 208 TUCPRS confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Update field_7i84u.hal because it currently uses input-00 | [RECON 2026-08-08 §F: PRS-9 line 209 TCPRS confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
+          <t xml:space="preserve">RESOLVED - field_7i84u.hal binds tool-clamped to input-15 | [RECON 2026-08-08 §F: PRS-9 line 209 TCPRS confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add HAL net when confirmed | [RECON 2026-08-08 §F: PRS-10 line 210 HGPRS = HIGH gear confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/orient_ladder_transcription.md]</t>
+          <t xml:space="preserve">HAL net bound in atc_orient.hal | [RECON 2026-08-08 §F: PRS-10 line 210 HGPRS = HIGH gear confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/orient_ladder_transcription.md]</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add HAL net when confirmed | [RECON 2026-08-08 §F: PRS-12 line 212 LGPRS = LOW gear confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/orient_ladder_transcription.md]</t>
+          <t xml:space="preserve">HAL net bound in atc_orient.hal | [RECON 2026-08-08 §F: PRS-12 line 212 LGPRS = LOW gear confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/orient_ladder_transcription.md]</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add HAL net when confirmed | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
+          <t xml:space="preserve">HAL net bound in atc_orient.hal | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -20167,7 +20167,7 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify SOL-62 identification against parts list pp.85-91 | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/coolant_ladder_transcription.md] | [2026-08-12 CONFLICT: the OEM head placard (dwg 24136209710) disagrees with this solenoid identity - see wiring/authority_conflicts.md section 5 and wiring/head_device_placard.md. Nothing changed here; identity must be settled BEFORE RLY-5/6/7 are wired.] | [2026-08-13 IDENTIFIED: coil wire label read on the machine = 415 -&gt; SOL-15 SPINDLE AIR BLAST, matching connector_crossref (OEM pg90). The SOL-62 label on this row was WRONG. Function and wire were already correct, so the fix is a relabel not a rebinding. Owner approval pending. See wiring/authority_conflicts.md section 5] | [2026-08-13 APPLIED (owner approved): field point corrected SOL-62 -&gt; SOL-15. Coil wire label read on the machine = 415 (RC3A side) / 215 (terminal-unit side, CN11-6). Function and wire were already correct - this was a relabel, not a rebinding. hal_net air-blast and the OUT3 binding are unchanged.]</t>
+          <t xml:space="preserve">[LADDER-REF 2026-08-10 (approved AG): docs/ladder/coolant_ladder_transcription.md] | [2026-08-12 CONFLICT: the OEM head placard (dwg 24136209710) disagrees with this solenoid identity - see wiring/authority_conflicts.md section 5 and wiring/head_device_placard.md. Nothing changed here; identity must be settled BEFORE RLY-5/6/7 are wired.] | [2026-08-13 IDENTIFIED: coil wire label read on the machine = 415 -&gt; SOL-15 SPINDLE AIR BLAST, matching connector_crossref (OEM pg90). The SOL-62 label on this row was WRONG. Function and wire were already correct, so the fix is a relabel not a rebinding. Owner approval pending. See wiring/authority_conflicts.md section 5] | [2026-08-13 APPLIED (owner approved): field point corrected SOL-62 -&gt; SOL-15. Coil wire label read on the machine = 415 (RC3A side) / 215 (terminal-unit side, CN11-6). Function and wire were already correct - this was a relabel, not a rebinding. hal_net air-blast and the OUT3 binding are unchanged.]</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
@@ -20259,7 +20259,7 @@
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t xml:space="preserve">MMS touch-sensor air jet | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/coolant_ladder_transcription.md] | [2026-08-12 CONFLICT: the OEM head placard (dwg 24136209710) disagrees with this solenoid identity - see wiring/authority_conflicts.md section 5 and wiring/head_device_placard.md. Nothing changed here; identity must be settled BEFORE RLY-5/6/7 are wired.] | [2026-08-13 DEVICE NOT FITTED: owner confirms only two air solenoids exist on the head (415=SOL-15, 416=SOL-16) and there are no hidden ones. This row was labelled SOL-35 (dust inhole eliminate); neither SOL-35 nor SOL-61 (air jet) is on the head. SOL-61 serves the MMS touch sensor, already flagged OPTION_VERIFY. RECOMMEND NOT_USED/RESERVED - do not fit RLY-6. Owner decision. See authority_conflicts.md section 5] | [2026-08-13 REPURPOSED (owner approved): was TOUCH_SENSOR_BLAST / SOL-35. That device (MMS touch-sensor air jet, SOL-61) is NOT FITTED on this machine - only SOL-15 and SOL-16 exist on the head. This terminal is reallocated to SOL-16 WORK AIR BLAST, which IS fitted and wired (coil label 416 / CN11-7 wire 216) but previously had no authority row. RESERVED with hal_net none per the MANUAL_TOOL_CLAMP_PB precedent: real device, not yet field-verified, so deliberately HAL-unbound. Bind it once RLY-6 is fitted and the wire is confirmed.]</t>
+          <t xml:space="preserve">[LADDER-REF 2026-08-10 (approved AG): docs/ladder/coolant_ladder_transcription.md] | [2026-08-12 CONFLICT: the OEM head placard (dwg 24136209710) disagrees with this solenoid identity - see wiring/authority_conflicts.md section 5 and wiring/head_device_placard.md. Nothing changed here; identity must be settled BEFORE RLY-5/6/7 are wired.] | [2026-08-13 DEVICE NOT FITTED: owner confirms only two air solenoids exist on the head (415=SOL-15, 416=SOL-16) and there are no hidden ones. This row was labelled SOL-35 (dust inhole eliminate); neither SOL-35 nor SOL-61 (air jet) is on the head. SOL-61 serves the MMS touch sensor, already flagged OPTION_VERIFY. RECOMMEND NOT_USED/RESERVED - do not fit RLY-6. Owner decision. See authority_conflicts.md section 5] | [2026-08-13 REPURPOSED (owner approved): was TOUCH_SENSOR_BLAST / SOL-35. That device (MMS touch-sensor air jet, SOL-61) is NOT FITTED on this machine - only SOL-15 and SOL-16 exist on the head. This terminal is reallocated to SOL-16 WORK AIR BLAST, which IS fitted and wired (coil label 416 / CN11-7 wire 216) but previously had no authority row. RESERVED with hal_net none per the MANUAL_TOOL_CLAMP_PB precedent: real device, not yet field-verified, so deliberately HAL-unbound. Bind it once RLY-6 is fitted and the wire is confirmed.]</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
@@ -33134,7 +33134,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMBIGUOUS 2026-08-10: CN11-6 (wire215 SPINDLE AIR BLAST) vs CN11-7 (wire216 WORK AIR BLAST) both plausible for SOL-62 (RLY-5) - no wire# for SOL-62 found to disambiguate; verify against parts list pp.85-91 before landing</t>
+          <t xml:space="preserve">AMBIGUOUS 2026-08-10: CN11-6 (wire215 SPINDLE AIR BLAST) vs CN11-7 (wire216 WORK AIR BLAST) both plausible for SOL-62 (RLY-5) - no wire# for SOL-62 found to disambiguate; verify against parts list pp.85-91 before landing [SUPERSEDED 2026-08-13: settled - CN11-6 wire 215/415 = SOL-15 spindle air blast</t>
         </is>
       </c>
     </row>
@@ -34030,7 +34030,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESOLVED 2026-08-10: BBIA-1 terminal-unit CN11 pin10 = wire261 AIR JET - matches 'MMS touch-sensor air jet' (SOL-35) exactly, the only air-jet entry on CN11</t>
+          <t xml:space="preserve">RESOLVED 2026-08-10: BBIA-1 terminal-unit CN11 pin10 = wire261 AIR JET - matches 'MMS touch-sensor air jet' exactly, the only air-jet entry on CN11 [SUPERSEDED 2026-08-13: wire 261 = SOL-61 air jet, not SOL-35; device not fitted on this machine and OUT4 reallocated to WORK_AIR_BLAST (SOL-16) - see wiring/authority_conflicts.md sec 5]</t>
         </is>
       </c>
     </row>
@@ -51963,7 +51963,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">probe-in</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -51978,7 +51978,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROPOSED</t>
+          <t xml:space="preserve">RESERVED</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/wiring/MESAC_Wiring_Crosswalk.xlsx
+++ b/wiring/MESAC_Wiring_Crosswalk.xlsx
@@ -144,7 +144,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">probe-in</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESERVED</t>
+          <t xml:space="preserve">PROPOSED</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESERVED 2026-08-21 (owner decision): probe out of scope per mesa/current_pin_authority.csv PROBE_SKIP1; hal_net none, TB3 IN15 spare. If re-scoped: continuity-trace the installed Renishaw MP-3 interface to CN200-3 and verify voltage, idle polarity, and fail-open behavior; MMS SKIP alone does not prove this is the retained probe conductor.</t>
+          <t xml:space="preserve">Continuity-trace the installed Renishaw MP-3 interface to CN200-3 and verify voltage, idle polarity, and fail-open behavior; MMS SKIP alone does not prove this is the retained probe conductor.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -2172,22 +2172,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE TIMER</t>
+          <t xml:space="preserve">WAY LUBE WARNING TIMER</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">lube</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNQ-36</t>
+          <t xml:space="preserve">CN3-36</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-W</t>
+          <t xml:space="preserve">CA4-V</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2264,27 +2264,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE FWD/REV SHIFTER</t>
+          <t xml:space="preserve">MACHINE POWER SUPPLY (X78 MPWS.M; fed by PS-1 hydraulic pressure switch per p133)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">safety</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNQ-37</t>
+          <t xml:space="preserve">CND4-47</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-V</t>
+          <t xml:space="preserve">CA4-W</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">OEM_SAFETY_RETAIN</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2314,12 +2314,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">OEM_SAFETY_RETAIN</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">No current Mesa authority row claims this conductor; review only if the OEM function is retained.</t>
+          <t xml:space="preserve">Retain in the untouched OEM safety circuit; no Mesa GPIO route.</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAG_BCD_BIT0</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 1</t>
+          <t xml:space="preserve">MANUAL MAGAZINE ROTATE PB (X07 TSPB.M)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2468,42 +2468,42 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MESA_ROUTE</t>
+          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7i84U-A</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB2</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN19</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag-bcd-bit0</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROUTE_DEFINED_FIELD_VERIFY</t>
+          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decode with bcd2s or custom mux | [RECON 2026-08-08 §F: PRS-21 line 221 confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE ROT POS 1, wire 150, CN2-4/CND2-4 (trusted over pg135 'wire 221' - that wire is BIT1 on the board).] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
+          <t xml:space="preserve">No current Mesa authority row claims this conductor; review only if the OEM function is retained.</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAG_BCD_BIT1</t>
+          <t xml:space="preserve">MAG_BCD_BIT0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 2</t>
+          <t xml:space="preserve">MAGAZINE POSITION 1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN20</t>
+          <t xml:space="preserve">IN19</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag-bcd-bit1</t>
+          <t xml:space="preserve">mag-bcd-bit0</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decode with bcd2s or custom mux | [RECON 2026-08-08 §F: PRS-22 line 222 confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE ROT POS 2, wire 221, CN2-5/CND2-5 (trusted over pg135 'wire 222').] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
+          <t xml:space="preserve">Decode with bcd2s or custom mux | [RECON 2026-08-08 §F: PRS-21 line 221 confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE ROT POS 1, wire 150, CN2-4/CND2-4 (trusted over pg135 'wire 221' - that wire is BIT1 on the board).] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md] | [2026-09-02 AUDIT (owner approved): the block was shifted one pin — p84 dwg 4143075321, pg135 dwg 4143075409 and p105 CA4 detail all agree: CN2-4/150 = MANUAL MAGAZINE ROTATE PB (X07 TSPB.M per p133); position bits 1/2/4/8/10 are CN2-5..9 wires 221-225; the 2026-08-09 PINOUT-RECONCILED override trusted a shifted transcription and is superseded. BIT0 corrected to CN2-5/221.]</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAG_BCD_BIT2</t>
+          <t xml:space="preserve">MAG_BCD_BIT1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 4</t>
+          <t xml:space="preserve">MAGAZINE POSITION 2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN21</t>
+          <t xml:space="preserve">IN20</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag-bcd-bit2</t>
+          <t xml:space="preserve">mag-bcd-bit1</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decode with bcd2s or custom mux | [RECON 2026-08-08 §F: PRS-23 line 223 confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE ROT POS 4, wire 222, CN2-6/CND2-6 (trusted over pg135 'wire 223').] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
+          <t xml:space="preserve">Decode with bcd2s or custom mux | [RECON 2026-08-08 §F: PRS-22 line 222 confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE ROT POS 2, wire 221, CN2-5/CND2-5 (trusted over pg135 'wire 222').] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md] | [2026-09-02 AUDIT (owner approved): block de-shifted — BIT1 = CN2-6/222 per p84 + pg135; 2026-08-09 override superseded.]</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAG_BCD_BIT3</t>
+          <t xml:space="preserve">MAG_BCD_BIT2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 8</t>
+          <t xml:space="preserve">MAGAZINE POSITION 4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN22</t>
+          <t xml:space="preserve">IN21</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag-bcd-bit3</t>
+          <t xml:space="preserve">mag-bcd-bit2</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decode with bcd2s or custom mux | [RECON 2026-08-08 §F: PRS-24 line 224 confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE ROT POS 8, wire 223, CN2-7/CND2-7 (trusted over pg135 'wire 224').] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
+          <t xml:space="preserve">Decode with bcd2s or custom mux | [RECON 2026-08-08 §F: PRS-23 line 223 confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE ROT POS 4, wire 222, CN2-6/CND2-6 (trusted over pg135 'wire 223').] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md] | [2026-09-02 AUDIT (owner approved): block de-shifted — BIT2 = CN2-7/223 per p84 + pg135; 2026-08-09 override superseded.]</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAG_BCD_BIT4</t>
+          <t xml:space="preserve">MAG_BCD_BIT3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 10</t>
+          <t xml:space="preserve">MAGAZINE POSITION 8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN23</t>
+          <t xml:space="preserve">IN22</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag-bcd-bit4</t>
+          <t xml:space="preserve">mag-bcd-bit3</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decode with bcd2s or custom mux | [RECON 2026-08-08 §F: PRS-25 line 225 confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE ROT POS 10, wire 224, CN2-8/CND2-8 (trusted over pg135 'wire 225'). NB: the field PRS-nn labels are pg135 PLC-side identities and may not match the board bit order - physical wire label is final.] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
+          <t xml:space="preserve">Decode with bcd2s or custom mux | [RECON 2026-08-08 §F: PRS-24 line 224 confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE ROT POS 8, wire 223, CN2-7/CND2-7 (trusted over pg135 'wire 224').] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md] | [2026-09-02 AUDIT (owner approved): block de-shifted — BIT3 = CN2-8/224 per p84 + pg135; 2026-08-09 override superseded.]</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAG_IN_POS</t>
+          <t xml:space="preserve">MAG_BCD_BIT4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE POSITION OK</t>
+          <t xml:space="preserve">MAGAZINE POSITION 10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2943,12 +2943,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN28</t>
+          <t xml:space="preserve">IN23</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag-in-pos</t>
+          <t xml:space="preserve">mag-bcd-bit4</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mandatory for magazine indexing (rungs 3401/33xx). Writer added in field_7i84u.hal (net mag-in-pos &lt;= input-28) on 2026-08-06. Verify prox type/polarity before commissioning. | [RECON 2026-08-08 CONFIRMED: MAG_IN_POS = PRS-13 MIPRS 'MAGAZINE INPOSITION' wire 213 X0D, Dwg 4143075409 pg135. In-position strobe; tool-# bits are PRS-21..25 (711P/712P/714P/718P/721P). Supersedes prior 'PRS-13=tool bit'.] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE POSITION OK, wire 225, CN2-9/CND2-9 (trusted). pg135 read the in-position prox as PRS-13/wire 213, but wire 213 appears in the BBIA-1 pinout only as the CN11-5 GEAR SHIFT LOW output, not on the CN2 input bank; POSITION OK is 225/CN2-9. PLC-side prox remains PRS-13/X00D.] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md]</t>
+          <t xml:space="preserve">Decode with bcd2s or custom mux | [RECON 2026-08-08 §F: PRS-25 line 225 confirmed by Dwg 4143075409 (Motion Switch Input 3)] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE ROT POS 10, wire 224, CN2-8/CND2-8 (trusted over pg135 'wire 225'). NB: the field PRS-nn labels are pg135 PLC-side identities and may not match the board bit order - physical wire label is final.] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md] | [2026-09-02 AUDIT (owner approved): block de-shifted — BIT4 = CN2-9/225 per p84 + pg135; 2026-08-09 override superseded.]</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MAG_IN_POS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">218</t>
+          <t xml:space="preserve">213</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE POWER OPEN</t>
+          <t xml:space="preserve">MAGAZINE INPOSITION (MIPRS PRS-13)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3020,42 +3020,42 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">MESA_ROUTE</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">7i84U-A</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">TB2</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">IN28</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">mag-in-pos</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNALLOCATED</t>
+          <t xml:space="preserve">FACTORY_INTERFACE</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">ROUTE_DEFINED_FIELD_VERIFY</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t xml:space="preserve">No current Mesa authority row claims this conductor; review only if the OEM function is retained.</t>
+          <t xml:space="preserve">Mandatory for magazine indexing (rungs 3401/33xx). Writer added in field_7i84u.hal (net mag-in-pos &lt;= input-28) on 2026-08-06. Verify prox type/polarity before commissioning. | [RECON 2026-08-08 CONFIRMED: MAG_IN_POS = PRS-13 MIPRS 'MAGAZINE INPOSITION' wire 213 X0D, Dwg 4143075409 pg135. In-position strobe; tool-# bits are PRS-21..25 (711P/712P/714P/718P/721P). Supersedes prior 'PRS-13=tool bit'.] | [PINOUT-RECONCILED 2026-08-09: BBIA-1 board = MAGAZINE POSITION OK, wire 225, CN2-9/CND2-9 (trusted). pg135 read the in-position prox as PRS-13/wire 213, but wire 213 appears in the BBIA-1 pinout only as the CN11-5 GEAR SHIFT LOW output, not on the CN2 input bank; POSITION OK is 225/CN2-9. PLC-side prox remains PRS-13/X00D.] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/atc_ladder_transcription.md] | [2026-09-02 AUDIT (owner approved): block de-shifted — in-position strobe = CN2-10 wire 213 (MIPRS, PRS-13; p105 CA4-F = 213) per p84 + pg135 + p105; CN2-9/225 is the position-10 bit (now MAG_BCD_BIT4). The 2026-08-09 PINOUT-RECONCILED override is superseded.]</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">+LTZ</t>
+          <t xml:space="preserve">+LY2</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z-AXIS OVER TRAVEL</t>
+          <t xml:space="preserve">2nd +Y OVER TRAVEL (PRS-55; to relay 1237/PYOT)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-12</t>
+          <t xml:space="preserve">1-12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-L</t>
+          <t xml:space="preserve">CA4-e</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOOL MEASURE DEVICE TIMER</t>
+          <t xml:space="preserve">TOOL MEASURING ARM EXTEND</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">345</t>
+          <t xml:space="preserve">343</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOOL MEASURE DEVICE SW</t>
+          <t xml:space="preserve">TOOL MEASURING ARM RETRACT</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5387,17 +5387,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">362</t>
+          <t xml:space="preserve">238</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE LUBE TIMER</t>
+          <t xml:space="preserve">TOOL LENGTH MEASURE DEC.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">lube</t>
+          <t xml:space="preserve">probe</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE LUBE PRESS SW</t>
+          <t xml:space="preserve">TOOL MEASURE SKIP</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">lube</t>
+          <t xml:space="preserve">probe</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOOR_INTERLOCK</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">238</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5591,47 +5591,47 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-N</t>
+          <t xml:space="preserve">CA4-U</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">MESA_ROUTE</t>
+          <t xml:space="preserve">OEM_SAFETY_RETAIN</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7i84U-A</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB2</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN24</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">door-interlock</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROUTE_DEFINED_FIELD_VERIFY</t>
+          <t xml:space="preserve">OEM_SAFETY_RETAIN</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Series-wired 2026-08-03: X01D ITMDSS consolidated with LS-140/141 pair. Choose door-open versus door-closed net after normal state is measured. | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/estop_ladder_transcription.md]</t>
+          <t xml:space="preserve">Retain in the untouched OEM safety circuit; no Mesa GPIO route.</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPARE INPUT 2</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK 2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">spare</t>
+          <t xml:space="preserve">safety</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">OEM_SPARE_CONDUCTOR</t>
+          <t xml:space="preserve">OEM_SAFETY_RETAIN</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t xml:space="preserve">OEM_SPARE_CONDUCTOR</t>
+          <t xml:space="preserve">OEM_SAFETY_RETAIN</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t xml:space="preserve">A factory spare conductor exists; insulate and preserve its identity unless a reviewed revision deliberately repurposes it.</t>
+          <t xml:space="preserve">Retain in the untouched OEM safety circuit; no Mesa GPIO route.</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">EHB</t>
+          <t xml:space="preserve">EMB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN5-44</t>
+          <t xml:space="preserve">CN5-4</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CN5-5</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE TOOL CLAMP OK</t>
+          <t xml:space="preserve">SPINDLE TOOL DETECTOR</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6031,22 +6031,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">524</t>
+          <t xml:space="preserve">G24</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC24V SELECTOR (X Y Z 4 5 6)</t>
+          <t xml:space="preserve">DC24V -COM (ELECTRICAL CAB)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">selector</t>
+          <t xml:space="preserve">common</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-5</t>
+          <t xml:space="preserve">CN5-8</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">OEM_POWER_OR_COMMON</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">OEM_POWER_OR_COMMON</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t xml:space="preserve">No current Mesa authority row claims this conductor; review only if the OEM function is retained.</t>
+          <t xml:space="preserve">Do not assign to a signal input/output; preserve the documented electrical domain and verify rail disposition separately.</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6215,17 +6215,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">CP24</t>
+          <t xml:space="preserve">CH24</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEED HOLD SW (LATCH)</t>
+          <t xml:space="preserve">HEAD LUBE PRESS ALARM</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">operator</t>
+          <t xml:space="preserve">lube</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-H</t>
+          <t xml:space="preserve">CA4-j</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">COOLANT_LOW</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7135,17 +7135,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">232</t>
+          <t xml:space="preserve">-LZ2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2nd-S LEVEL</t>
+          <t xml:space="preserve">2nd -Z OVER TRAVEL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">coolant lvl</t>
+          <t xml:space="preserve">limit</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7160,42 +7160,42 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">MESA_ROUTE</t>
+          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7i84U-A</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB2</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN26</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">coolant-low</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROUTE_DEFINED_FIELD_VERIFY</t>
+          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net name follows HAL (polarity assumption: low = warning). Verify normal-state polarity in cabinet before promoting. | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/coolant_ladder_transcription.md]</t>
+          <t xml:space="preserve">No current Mesa authority row claims this conductor; review only if the OEM function is retained.</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">233</t>
+          <t xml:space="preserve">355</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXTERNAL TRIP PROTECTOR</t>
+          <t xml:space="preserve">THERMAL TRIP PROTECTOR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN23-14</t>
+          <t xml:space="preserve">CND4-46</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB1-31</t>
+          <t xml:space="preserve">TB1-144</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">OVER RUN EMG STOP</t>
+          <t xml:space="preserve">MAIN TRANSF. OVER HEAT</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-30</t>
+          <t xml:space="preserve">4-50</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN5-5</t>
+          <t xml:space="preserve">CN2-41</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-44</t>
+          <t xml:space="preserve">CND2-7</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9711,32 +9711,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISP1</t>
+          <t xml:space="preserve">DINTCSS</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-AXIS LINC INTERLOCK CANCEL</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK CANCEL (SS-51 selector; X1D)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4th axis</t>
+          <t xml:space="preserve">safety</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-37</t>
+          <t xml:space="preserve">1-37</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB1-33</t>
+          <t xml:space="preserve">TB1-151</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">OEM_SAFETY_RETAIN</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">OEM_SAFETY_RETAIN</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t xml:space="preserve">No current Mesa authority row claims this conductor; review only if the OEM function is retained.</t>
+          <t xml:space="preserve">Retain in the untouched OEM safety circuit; no Mesa GPIO route.</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9803,22 +9803,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">XYZR4</t>
+          <t xml:space="preserve">*DEC4</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-AXIS UNCLAMP INTERLOCK CANCEL</t>
+          <t xml:space="preserve">4 AXIS ZERO RETURN DEC.</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4th axis</t>
+          <t xml:space="preserve">homing</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-14</t>
+          <t xml:space="preserve">4-44</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-AXIS LIMIT OVER-TRAVEL RELEASE</t>
+          <t xml:space="preserve">INDEX TABLE TYPE 4-AXIS UNCLAMPED (LS)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -9987,17 +9987,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1NRAILS</t>
+          <t xml:space="preserve">INHRLS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE REAR L.S.</t>
+          <t xml:space="preserve">INHIBIT READ LS</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">NC iface</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">-1NRAILS</t>
+          <t xml:space="preserve">-INHRLS</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -10452,22 +10452,22 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYCLE FINISH</t>
+          <t xml:space="preserve">PATO LIGHT (patrol light)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">NC iface</t>
+          <t xml:space="preserve">aux</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-16</t>
+          <t xml:space="preserve">CND23-29</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">CV-29</t>
+          <t xml:space="preserve">CN301A-1</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -10539,22 +10539,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYFIN</t>
+          <t xml:space="preserve">M44T</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYCLE FINISH (2)</t>
+          <t xml:space="preserve">mag M44T</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">NC iface</t>
+          <t xml:space="preserve">ATC</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-29</t>
+          <t xml:space="preserve">3-48</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">MA3T</t>
+          <t xml:space="preserve">M43T</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-48</t>
+          <t xml:space="preserve">3-49</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">MA3T</t>
+          <t xml:space="preserve">M45T</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-49</t>
+          <t xml:space="preserve">3-45</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10815,22 +10815,22 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">MA3T</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag M45T</t>
+          <t xml:space="preserve">(not used - blank on source table)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">spare</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-45</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">NO_CONNECTION</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">NO_CONNECTION</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t xml:space="preserve">No current Mesa authority row claims this conductor; review only if the OEM function is retained.</t>
+          <t xml:space="preserve">No conductor to land; positively unused on the cited OEM table.</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOW GEAR OVER TRAVEL</t>
+          <t xml:space="preserve">LOW GEAR SELECT</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">+LYZ</t>
+          <t xml:space="preserve">+LY2</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">+YZ OVER TRAVEL</t>
+          <t xml:space="preserve">+Y 2nd OVER TRAVEL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-LYZ</t>
+          <t xml:space="preserve">-LZ2</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-YZ OVER TRAVEL</t>
+          <t xml:space="preserve">-Z 2nd OVER TRAVEL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAIN PANE POWER ON</t>
+          <t xml:space="preserve">DC24V +COM (MACHINE)</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">power</t>
+          <t xml:space="preserve">common</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN12-21</t>
+          <t xml:space="preserve">CN2-21</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">238</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -12563,22 +12563,22 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">241</t>
+          <t xml:space="preserve">340</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">POWER ON MAIN LAMP INTERLOCK</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK 2</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">power</t>
+          <t xml:space="preserve">safety</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-23</t>
+          <t xml:space="preserve">CN2-39</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">OEM_POWER_OR_COMMON</t>
+          <t xml:space="preserve">OEM_SAFETY_RETAIN</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t xml:space="preserve">OEM_POWER_OR_COMMON</t>
+          <t xml:space="preserve">OEM_SAFETY_RETAIN</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do not assign to a signal input/output; preserve the documented electrical domain and verify rail disposition separately.</t>
+          <t xml:space="preserve">Retain in the untouched OEM safety circuit; no Mesa GPIO route.</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12655,22 +12655,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">main lamp interlock 2</t>
+          <t xml:space="preserve">(not used - blank on source table)</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">power</t>
+          <t xml:space="preserve">spare</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">-39</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">OEM_POWER_OR_COMMON</t>
+          <t xml:space="preserve">NO_CONNECTION</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t xml:space="preserve">OEM_POWER_OR_COMMON</t>
+          <t xml:space="preserve">NO_CONNECTION</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do not assign to a signal input/output; preserve the documented electrical domain and verify rail disposition separately.</t>
+          <t xml:space="preserve">No conductor to land; positively unused on the cited OEM table.</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12747,12 +12747,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">ES1</t>
+          <t xml:space="preserve">ZS1</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE SPEED</t>
+          <t xml:space="preserve">SPINDLE ZERO SPEED</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-1</t>
+          <t xml:space="preserve">CN4-1</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVO_FAULT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -12839,22 +12839,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">SER</t>
+          <t xml:space="preserve">SFR</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVO ERROR</t>
+          <t xml:space="preserve">SPINDLE FORWARD</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">servo</t>
+          <t xml:space="preserve">spindle</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-13</t>
+          <t xml:space="preserve">3-14</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12864,42 +12864,42 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">MESA_ROUTE</t>
+          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">7i84U-A</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB3</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN10</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t xml:space="preserve">servo-fault</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROUTE_DEFINED_FIELD_VERIFY</t>
+          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owner decision 2026-08-11 (AG): OEM SER is ONE combined servo-error contact for all axes (only one SER line on the 50-pin CN6) not per-axis; IN10 fans out to all three joint amp-faults; IN11/IN12 freed to spare. Bench-verify HD81/HD101 ALM polarity before enabling | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/estop_ladder_transcription.md]</t>
+          <t xml:space="preserve">No current Mesa authority row claims this conductor; review only if the OEM function is retained.</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE SERVO</t>
+          <t xml:space="preserve">SPINDLE REVERSE</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE READY</t>
+          <t xml:space="preserve">SPINDLE RUN</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -13120,7 +13120,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUN COMMAND</t>
+          <t xml:space="preserve">ORIENT COMMAND</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">T-CODE NO MEMORY</t>
+          <t xml:space="preserve">TOOL CHANGE MEMORY</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN12-1</t>
+          <t xml:space="preserve">CND23-49</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -13483,12 +13483,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">NSFT</t>
+          <t xml:space="preserve">NSPT</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">NG TOOL</t>
+          <t xml:space="preserve">NO SPARE TOOL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE OIL TOOL DETECTOR</t>
+          <t xml:space="preserve">MAGAZINE TOOL DETECTOR</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE HEAD LUBE PRESSURE</t>
+          <t xml:space="preserve">HEAD LUBE PRESSURE</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -13958,7 +13958,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN11-6</t>
+          <t xml:space="preserve">CN1-6</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -14960,7 +14960,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE SPINDLE TOOL DETECTOR</t>
+          <t xml:space="preserve">SPINDLE TOOL DETECTOR</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN12-42</t>
+          <t xml:space="preserve">CN2-42</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -15047,12 +15047,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">EHB</t>
+          <t xml:space="preserve">*ESP</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMERGENCY STOP</t>
+          <t xml:space="preserve">EMERGENCY STOP (chain status to NC X000)</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN5-43</t>
+          <t xml:space="preserve">CND1-3</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -15139,12 +15139,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">141</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEAD LUBE PRESSURE</t>
+          <t xml:space="preserve">HEAD LUBE PRESSURE ALARM</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-28</t>
+          <t xml:space="preserve">4-48</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN6-51</t>
+          <t xml:space="preserve">CN4-6</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN6-8</t>
+          <t xml:space="preserve">CN4-8</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -15890,7 +15890,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN6-7</t>
+          <t xml:space="preserve">CN4-7</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN6-9</t>
+          <t xml:space="preserve">CN4-9</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN6-10</t>
+          <t xml:space="preserve">CN4-10</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORIENT LOOP CHECK</t>
+          <t xml:space="preserve">LOW GEAR SHIFT</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-13</t>
+          <t xml:space="preserve">CN4-13</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -18528,7 +18528,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC_ZONE_Z</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -18548,12 +18548,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">OIL TEMP DETECTOR</t>
+          <t xml:space="preserve">TOOL DETECTOR (MGTDPRS X05)</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">alarm</t>
+          <t xml:space="preserve">ATC</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -18563,37 +18563,37 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-0503</t>
+          <t xml:space="preserve">TB503-b11</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t xml:space="preserve">MESA_ROUTE</t>
+          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">7i84U-A</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB3</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN1</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t xml:space="preserve">atc-z-zone</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -18988,7 +18988,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC_ZONE_Y</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -19008,52 +19008,52 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE TIMER</t>
+          <t xml:space="preserve">SPINDLE TOOL DETECTOR (SPTDPRS X5B)</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">spindle</t>
+          <t xml:space="preserve">ATC</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-44</t>
+          <t xml:space="preserve">4-26</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D1 1-14</t>
+          <t xml:space="preserve">TB504-0101</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t xml:space="preserve">MESA_ROUTE</t>
+          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">7i84U-A</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB3</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN0</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t xml:space="preserve">atc-y-zone</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">208B</t>
+          <t xml:space="preserve">708B</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -19739,7 +19739,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">208A</t>
+          <t xml:space="preserve">708A</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -20015,7 +20015,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">213</t>
+          <t xml:space="preserve">713</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -20075,7 +20075,7 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conflict: connector_crossref.md omits SOL-12 and identifies SOL-13 as low; verify both gear-shift coils before wiring | [RECON 2026-08-08 §G: SWAPPED SOL-12-&gt;SOL-13 per Dwg 41431075414 p140 + element list Y00C GSL.M=SOL-13=LOW; HOLD_CONFLICT cleared] | [CONFIRMED 2026-08-08: pg100 TB-51 (Dwg 4143075338) wire 413-&gt;SOL-13-&gt;GEAR SHIFT LOW; physical double-check of §G swap complete] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/orient_ladder_transcription.md] | [2026-08-13 CONFIRMED: wire 413 read at the RIGHT coil of the same Nachi SA-G01-E3X-C1-31 valve = SOL-13 gear shift low. Both gear coils are on ONE 3-position valve]</t>
+          <t xml:space="preserve">Conflict: connector_crossref.md omits SOL-12 and identifies SOL-13 as low; verify both gear-shift coils before wiring | [RECON 2026-08-08 §G: SWAPPED SOL-12-&gt;SOL-13 per Dwg 41431075414 p140 + element list Y00C GSL.M=SOL-13=LOW; HOLD_CONFLICT cleared] | [CONFIRMED 2026-08-08: pg100 TB-51 (Dwg 4143075338) wire 413-&gt;SOL-13-&gt;GEAR SHIFT LOW; physical double-check of §G swap complete] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/orient_ladder_transcription.md] | [2026-08-13 CONFIRMED: wire 413 read at the RIGHT coil of the same Nachi SA-G01-E3X-C1-31 valve = SOL-13 gear shift low. Both gear coils are on ONE 3-position valve] | [2026-09-02 AUDIT (owner approved): T.U.-side wire corrected 213 -&gt; 713 per p85 + p140 (7-&gt;2 digit misread family; wire 213 is the CN2-10 magazine in-position input). Solenoid-side 413 unchanged.]</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
@@ -20107,7 +20107,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">215</t>
+          <t xml:space="preserve">715</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -20167,7 +20167,7 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t xml:space="preserve">[LADDER-REF 2026-08-10 (approved AG): docs/ladder/coolant_ladder_transcription.md] | [2026-08-12 CONFLICT: the OEM head placard (dwg 24136209710) disagrees with this solenoid identity - see wiring/authority_conflicts.md section 5 and wiring/head_device_placard.md. Nothing changed here; identity must be settled BEFORE RLY-5/6/7 are wired.] | [2026-08-13 IDENTIFIED: coil wire label read on the machine = 415 -&gt; SOL-15 SPINDLE AIR BLAST, matching connector_crossref (OEM pg90). The SOL-62 label on this row was WRONG. Function and wire were already correct, so the fix is a relabel not a rebinding. Owner approval pending. See wiring/authority_conflicts.md section 5] | [2026-08-13 APPLIED (owner approved): field point corrected SOL-62 -&gt; SOL-15. Coil wire label read on the machine = 415 (RC3A side) / 215 (terminal-unit side, CN11-6). Function and wire were already correct - this was a relabel, not a rebinding. hal_net air-blast and the OUT3 binding are unchanged.]</t>
+          <t xml:space="preserve">[LADDER-REF 2026-08-10 (approved AG): docs/ladder/coolant_ladder_transcription.md] | [2026-08-12 CONFLICT: the OEM head placard (dwg 24136209710) disagrees with this solenoid identity - see wiring/authority_conflicts.md section 5 and wiring/head_device_placard.md. Nothing changed here; identity must be settled BEFORE RLY-5/6/7 are wired.] | [2026-08-13 IDENTIFIED: coil wire label read on the machine = 415 -&gt; SOL-15 SPINDLE AIR BLAST, matching connector_crossref (OEM pg90). The SOL-62 label on this row was WRONG. Function and wire were already correct, so the fix is a relabel not a rebinding. Owner approval pending. See wiring/authority_conflicts.md section 5] | [2026-08-13 APPLIED (owner approved): field point corrected SOL-62 -&gt; SOL-15. Coil wire label read on the machine = 415 (RC3A side) / 715 (terminal-unit side, CN11-6). Function and wire were already correct - this was a relabel, not a rebinding. hal_net air-blast and the OUT3 binding are unchanged.] | [2026-09-02 AUDIT (owner approved): T.U.-side wire corrected 215 -&gt; 715 per p85 + p140 (7-&gt;2 misread family). Solenoid-side 415 (machine-read) unchanged.]</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">216</t>
+          <t xml:space="preserve">716</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -20259,7 +20259,7 @@
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t xml:space="preserve">[LADDER-REF 2026-08-10 (approved AG): docs/ladder/coolant_ladder_transcription.md] | [2026-08-12 CONFLICT: the OEM head placard (dwg 24136209710) disagrees with this solenoid identity - see wiring/authority_conflicts.md section 5 and wiring/head_device_placard.md. Nothing changed here; identity must be settled BEFORE RLY-5/6/7 are wired.] | [2026-08-13 DEVICE NOT FITTED: owner confirms only two air solenoids exist on the head (415=SOL-15, 416=SOL-16) and there are no hidden ones. This row was labelled SOL-35 (dust inhole eliminate); neither SOL-35 nor SOL-61 (air jet) is on the head. SOL-61 serves the MMS touch sensor, already flagged OPTION_VERIFY. RECOMMEND NOT_USED/RESERVED - do not fit RLY-6. Owner decision. See authority_conflicts.md section 5] | [2026-08-13 REPURPOSED (owner approved): was TOUCH_SENSOR_BLAST / SOL-35. That device (MMS touch-sensor air jet, SOL-61) is NOT FITTED on this machine - only SOL-15 and SOL-16 exist on the head. This terminal is reallocated to SOL-16 WORK AIR BLAST, which IS fitted and wired (coil label 416 / CN11-7 wire 216) but previously had no authority row. RESERVED with hal_net none per the MANUAL_TOOL_CLAMP_PB precedent: real device, not yet field-verified, so deliberately HAL-unbound. Bind it once RLY-6 is fitted and the wire is confirmed.]</t>
+          <t xml:space="preserve">[LADDER-REF 2026-08-10 (approved AG): docs/ladder/coolant_ladder_transcription.md] | [2026-08-12 CONFLICT: the OEM head placard (dwg 24136209710) disagrees with this solenoid identity - see wiring/authority_conflicts.md section 5 and wiring/head_device_placard.md. Nothing changed here; identity must be settled BEFORE RLY-5/6/7 are wired.] | [2026-08-13 DEVICE NOT FITTED: owner confirms only two air solenoids exist on the head (415=SOL-15, 416=SOL-16) and there are no hidden ones. This row was labelled SOL-35 (dust inhole eliminate); neither SOL-35 nor SOL-61 (air jet) is on the head. SOL-61 serves the MMS touch sensor, already flagged OPTION_VERIFY. RECOMMEND NOT_USED/RESERVED - do not fit RLY-6. Owner decision. See authority_conflicts.md section 5] | [2026-08-13 REPURPOSED (owner approved): was TOUCH_SENSOR_BLAST / SOL-35. That device (MMS touch-sensor air jet, SOL-61) is NOT FITTED on this machine - only SOL-15 and SOL-16 exist on the head. This terminal is reallocated to SOL-16 WORK AIR BLAST, which IS fitted and wired (coil label 416 / CN11-7 wire 716) but previously had no authority row. RESERVED with hal_net none per the MANUAL_TOOL_CLAMP_PB precedent: real device, not yet field-verified, so deliberately HAL-unbound. Bind it once RLY-6 is fitted and the wire is confirmed.] | [2026-09-02 AUDIT (owner approved): T.U.-side wire corrected 216 -&gt; 716 per p85 + p140 (7-&gt;2 misread family). Solenoid-side 416 (machine-read) unchanged.]</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">217</t>
+          <t xml:space="preserve">717</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -20383,7 +20383,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">262</t>
+          <t xml:space="preserve">762</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -20475,7 +20475,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">261</t>
+          <t xml:space="preserve">761</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -20567,7 +20567,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">735</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">236</t>
+          <t xml:space="preserve">736</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">731</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOL-31 confirmed via TB-51 diagram. Separate from OUT11 pump on 7i84U-A. | [RECON 2026-08-08 §C: Y011 FCL valve genuinely distinct from Y010 FCM motor; Y012 THC through-hole separate] | [RECON 2026-08-08 follow-up: status PROPOSED -&gt; COMMISSIONING_PENDING per §C element-list confirm] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/coolant_ladder_transcription.md]</t>
+          <t xml:space="preserve">SOL-31 confirmed via TB-51 diagram. Separate from OUT11 pump on 7i84U-A. | [RECON 2026-08-08 §C: Y011 FCL valve genuinely distinct from Y010 FCM motor; Y012 THC through-hole separate] | [RECON 2026-08-08 follow-up: status PROPOSED -&gt; COMMISSIONING_PENDING per §C element-list confirm] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/coolant_ladder_transcription.md] | [2026-09-02 AUDIT (owner approved): T.U.-side wire corrected 231 -&gt; 731 per p85 + p140 (7-&gt;2 misread family; dissolves the sec-7.1 "wire 231 reuse" question). Solenoid-side 431.]</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
@@ -20843,7 +20843,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">227</t>
+          <t xml:space="preserve">727</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">COOLANT_ON</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -20935,12 +20935,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">236</t>
+          <t xml:space="preserve">736</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLOOD COOLANT MOTOR STARTER</t>
+          <t xml:space="preserve">FLOOD COOLANT MOTOR STARTER (p85 reads 736; p140/p78 read 836 - jacket read decides)</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -20960,42 +20960,42 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t xml:space="preserve">MESA_ROUTE</t>
+          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">7i84U-A</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB2</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT11</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t xml:space="preserve">flood-coolant</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROUTE_DEFINED_FIELD_VERIFY</t>
+          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t xml:space="preserve">May need interposing relay | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/coolant_ladder_transcription.md]</t>
+          <t xml:space="preserve">No current Mesa authority row claims this conductor; review only if the OEM function is retained.</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
@@ -21027,7 +21027,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">835</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -21087,7 +21087,7 @@
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required before clamp/gear/ATC; interposing relay for contactor coil; prove HYD_PRESS_OK after start | [RECON 2026-08-08 §A: element list confirms Y096 HYD.M combined hydraulic + head-lube pump on 060231] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/estop_ladder_transcription.md]</t>
+          <t xml:space="preserve">Required before clamp/gear/ATC; interposing relay for contactor coil; prove HYD_PRESS_OK after start | [RECON 2026-08-08 §A: element list confirms Y096 HYD.M combined hydraulic + head-lube pump on 060231] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/estop_ladder_transcription.md] | [2026-09-02 AUDIT (owner approved): T.U.-side wire corrected 235 -&gt; 835 per p85 + p140 + p78 (7/8-&gt;2 misread family; dissolves the sec-7.1 "235/236 duplication").]</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
@@ -23327,7 +23327,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">ZS1</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -23347,7 +23347,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON 4-3</t>
+          <t xml:space="preserve">CON1-3</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -23419,7 +23419,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS2</t>
+          <t xml:space="preserve">ZS2</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE REV ROLLER THERMAL</t>
+          <t xml:space="preserve">SPINDLE CONTROLLER NORMAL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -24692,7 +24692,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE_ORIENT_ARRIVAL</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -24707,12 +24707,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">SETA</t>
+          <t xml:space="preserve">ORA1</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">set A</t>
+          <t xml:space="preserve">SPINDLE ORIENT ARRIVAL</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -24732,42 +24732,42 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t xml:space="preserve">MESA_ROUTE</t>
+          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">7i84U-A</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB3</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN4</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t xml:space="preserve">spindle-oriented</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROUTE_DEFINED_FIELD_VERIFY</t>
+          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
         </is>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC cannot cycle without orient; confirm FR-SX terminal and polarity | [RECON 2026-08-08 §A: element list confirms X003 ORA1 'ORIENT ARRIVAL' (ladder 3006/4810/5509) on 060231] | [RECON 2026-08-08 §D: FR-SX OBA1(t22)/OBA2(t23) -&gt; CN4-16/CN4-17 (digits verify)] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/spindle_run_ladder_transcription.md]</t>
+          <t xml:space="preserve">No current Mesa authority row claims this conductor; review only if the OEM function is retained.</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -24799,12 +24799,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">SETB</t>
+          <t xml:space="preserve">ORA2</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">set B</t>
+          <t xml:space="preserve">SPINDLE ORIENT ARRIVAL (2)</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -32730,17 +32730,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CND2-4</t>
+          <t xml:space="preserve">CND2-5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">150</t>
+          <t xml:space="preserve">221</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-4</t>
+          <t xml:space="preserve">CN2-5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -32750,7 +32750,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">BBIA-1 board pinout (trusted over pg135)</t>
+          <t xml:space="preserve">2026-09-02 AUDIT: block de-shifted per p84+pg135+p105 (CN2-4/150 is the manual-rotate PB); pg135 was right all along</t>
         </is>
       </c>
     </row>
@@ -32762,17 +32762,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CND2-5</t>
+          <t xml:space="preserve">CND2-6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">221</t>
+          <t xml:space="preserve">222</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-5</t>
+          <t xml:space="preserve">CN2-6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -32782,7 +32782,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BBIA-1 board pinout (trusted over pg135)</t>
+          <t xml:space="preserve">2026-09-02 AUDIT: block de-shifted per p84+pg135</t>
         </is>
       </c>
     </row>
@@ -32794,17 +32794,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CND2-6</t>
+          <t xml:space="preserve">CND2-7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">222</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-6</t>
+          <t xml:space="preserve">CN2-7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -32814,7 +32814,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BBIA-1 board pinout (trusted over pg135)</t>
+          <t xml:space="preserve">2026-09-02 AUDIT: block de-shifted per p84+pg135</t>
         </is>
       </c>
     </row>
@@ -32826,17 +32826,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CND2-7</t>
+          <t xml:space="preserve">CND2-8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">224</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-7</t>
+          <t xml:space="preserve">CN2-8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -32846,7 +32846,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BBIA-1 board pinout (trusted over pg135)</t>
+          <t xml:space="preserve">2026-09-02 AUDIT: block de-shifted per p84+pg135</t>
         </is>
       </c>
     </row>
@@ -32858,17 +32858,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CND2-8</t>
+          <t xml:space="preserve">CND2-9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">224</t>
+          <t xml:space="preserve">225</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-8</t>
+          <t xml:space="preserve">CN2-9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -32878,7 +32878,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">BBIA-1 board pinout (trusted over pg135)</t>
+          <t xml:space="preserve">2026-09-02 AUDIT: block de-shifted per p84+pg135</t>
         </is>
       </c>
     </row>
@@ -32942,7 +32942,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BBIA-1 pinout: COVER OPEN at CN2-11 (wire 218 also lands CN2-10=POWER OPEN)</t>
+          <t xml:space="preserve">BBIA-1 pinout: COVER OPEN at CN2-11 (2026-09-02: the "wire 218 also lands CN2-10" duplicate was an artifact of the shifted block - CN2-10 is 213 MAGAZINE INPOSITION)</t>
         </is>
       </c>
     </row>
@@ -33023,7 +33023,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">ZS1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -33038,7 +33038,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">BBIA-1 board pinout (trusted over pg135)</t>
+          <t xml:space="preserve">2026-09-02 AUDIT: p84 CN4-1 = ZS1 (no numeric wire; "231" was a misread); p133 draws ZS1 feeding relay 1246 whose contact (wire 143 at CN3-4) drives X01 SZS.M — both circuits real; jacket read closes it</t>
         </is>
       </c>
     </row>
@@ -33198,7 +33198,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESOLVED 2026-08-10: Dwg 4143075409 pg135 '2nd +Y OVER TRAVEL' = PRS-55 wire +LY2 at T.U CN3-44 - matches authority CSV's PRS-55 citation exactly</t>
+          <t xml:space="preserve">RETRACTED 2026-09-02 (citation defect): Dwg 4143075409 pg135 shows '2nd +Y OVER TRAVEL' PRS-55 wire +LY2 at T.U CN2-14 (to relay 1237/PYOT), NOT CN3-44. Dwg 4143075321 p84 + 4143075408 p134 give CN3-44 = SPTD/SPTDPRS spindle tool detector (X05B). Do-not-land hold on IN0 stands; row pending re-disposition</t>
         </is>
       </c>
     </row>
@@ -33230,7 +33230,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESOLVED 2026-08-10: Dwg 4143075409 pg135 '2nd -Z OVER TRAVEL' = PRS-66 wire -LZ2 at T.U CN3-39 - matches authority CSV's PRS-66 citation exactly</t>
+          <t xml:space="preserve">RETRACTED 2026-09-02 (citation defect): Dwg 4143075409 pg135 shows '2nd -Z OVER TRAVEL' PRS-66 wire -LZ2 at T.U CN1-5 (to relay 1240/NZOT), NOT CN3-39. Dwg 4143075321 p84 + 4143075408 p134 give CN3-39 = wire 147 magazine tool detector (X05 MGTDPRS). Do-not-land hold on IN1 stands; row pending re-disposition</t>
         </is>
       </c>
     </row>
@@ -33262,7 +33262,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANDIDATE 2026-08-10: BBIA-1 board pinout CN1-5 = wire232 '2nd-S LEVEL' (function: coolant lvl) - plausible match for coolant level switch; not cross-checked against a ladder-side wire# this session, verify polarity/normal-state before commissioning</t>
+          <t xml:space="preserve">CANDIDATE 2026-08-10: BBIA-1 board pinout CN1-5 = wire232 '2nd-S LEVEL' (function: coolant lvl) - plausible match for coolant level switch; not cross-checked against a ladder-side wire# this session, verify polarity/normal-state before commissioning [SUPERSEDED 2026-09-02: p84 CN1-5 = -LZ2 2nd -Z over-travel (corroborated CN6-13, p135 relay 1240/NZOT); '232 / 2nd-S LEVEL' was a misread. COOLANT_LOW has no located conductor - find the tank float wiring at the cabinet]</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">236</t>
+          <t xml:space="preserve">736/836?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -33294,7 +33294,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESOLVED 2026-08-10: BBIA-1 terminal-unit CN11 pin15 = wire236 FLOOD COOLANT MOTOR STARTER, matching 'coolant pump relay' (motor starter = pump, distinct from FLOOD_VALVE at CN11-13). NB pin15 shares wire236 with pin12 OIL HOLE - a data-quality flag in the source CSV, not resolved here</t>
+          <t xml:space="preserve">RESOLVED 2026-08-10: BBIA-1 terminal-unit CN11 pin15 = wire236 FLOOD COOLANT MOTOR STARTER, matching 'coolant pump relay' (motor starter = pump, distinct from FLOOD_VALVE at CN11-13). NB pin15 shares wire236 with pin12 OIL HOLE - a data-quality flag in the source CSV, not resolved here [SUPERSEDED 2026-09-02: 2NN family was a 7-&gt;2 misread - pin 12 = 736 OIL HOLE; pin 15 reads 736 on p85 but 836 on p140/p78 (jacket read decides); the duplication dissolves]</t>
         </is>
       </c>
     </row>
@@ -33326,7 +33326,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESOLVED 2026-08-10 (primary): BBIA-1 board pinout CN2-38 = wire238 MACHINE DOOR INTERLOCK (mirrored at CN6-23, same wire# - internally consistent). ALT candidate: Dwg 4143075407 pg133 T.U CN3-3 wire142 MDINT.M (ladder-side finding, different wire#, not reconciled with the board pinout). Door-interlock chain is series-wired with LS-140/141 per open_issues.md so more than one physical contact may legitimately exist</t>
+          <t xml:space="preserve">RESOLVED 2026-08-10 (primary): BBIA-1 board pinout CN2-38 = wire238 MACHINE DOOR INTERLOCK (mirrored at CN6-23, same wire# - internally consistent). ALT candidate: Dwg 4143075407 pg133 T.U CN3-3 wire142 MDINT.M (ladder-side finding, different wire#, not reconciled with the board pinout). Door-interlock chain is series-wired with LS-140/141 per open_issues.md so more than one physical contact may legitimately exist [SUPERSEDED 2026-09-02: wire is 341 per p84 CN2-38 + p85 CN6-23 (400 DPI); 238 is CN2-36 tool-length-measure dec. Companion CN2-39/CN6-24 = 340 door interlock 2]</t>
         </is>
       </c>
     </row>
@@ -33343,7 +33343,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">731</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -33407,7 +33407,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">213</t>
+          <t xml:space="preserve">713</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -33471,7 +33471,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">835</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -33486,7 +33486,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">BBIA-1 terminal-unit CN11 pin16 (dwg 4113075022 sheet 85 / 41434WB p85) read 2026-08-10 - see wiring/bbia1_cn_pinouts.csv; NOT the SSR-board's own CN11 (see CN11-SSR)</t>
+          <t xml:space="preserve">BBIA-1 terminal-unit CN11 pin16 (dwg 4143075322 sheet 85 / 41434WB p85) read 2026-08-10 - see wiring/bbia1_cn_pinouts.csv; NOT the SSR-board's own CN11 (see CN11-SSR)</t>
         </is>
       </c>
     </row>
@@ -33498,17 +33498,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CND2-9</t>
+          <t xml:space="preserve">CND2-10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">225</t>
+          <t xml:space="preserve">213</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-9</t>
+          <t xml:space="preserve">CN2-10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -33518,7 +33518,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">BBIA-1 board pinout (trusted over pg135)</t>
+          <t xml:space="preserve">2026-09-02 AUDIT: in-position strobe is CN2-10 wire 213 (MIPRS PRS-13; p105 CA4-F=213) per p84+pg135+p105; the 2026-08-09 "trusted over pg135" override is superseded</t>
         </is>
       </c>
     </row>
@@ -33646,7 +33646,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESOLVED 2026-08-10: Dwg 4143075408 pg134 T.U CN4-3/CN4-4 = wire mnemonics FA/FC 'SPINDLE CONTROLLER NORMAL', matching the authority note's FR-SX FA(t11)/FC(t12); BBIA-1 board pinout CN4-3='FA' labels it SPINDLE REV ROLLER THERMAL (label differs, mnemonic matches - trusted). Land IN14 from CN4-3; CN4-4 is the common return</t>
+          <t xml:space="preserve">RESOLVED 2026-08-10: Dwg 4143075407 pg133 + Dwg 4143075321 p84 T.U CN4-3/CN4-4 = wire mnemonics FA/FC 'SPINDLE CONTROLLER NORMAL', matching the authority note's FR-SX FA(t11)/FC(t12); BBIA-1 board pinout CN4-3='FA' labels it SPINDLE REV ROLLER THERMAL (label differs, mnemonic matches - trusted). Land IN14 from CN4-3; CN4-4 is the common return</t>
         </is>
       </c>
     </row>
@@ -33695,7 +33695,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">SETA</t>
+          <t xml:space="preserve">ORA1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -33710,7 +33710,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOW CONFIDENCE 2026-08-10: pre-existing authority note flags this as unverified (FR-SX OBA1(t22)/OBA2(t23) -&gt; CN4-16/CN4-17, 'digits verify'); BBIA-1 board pinout shows CN4-16/17 labeled SETA/SETB not OBA1/OBA2 - functionally plausible (orient-arrival confirmation bits) but not independently corroborated by wire# or a dedicated schematic row this session. Field-verify before commissioning</t>
+          <t xml:space="preserve">RESOLVED 2026-09-02: p84 at 560 DPI reads CN4-16/17 = ORA1/ORA2 'SPINDLE ORIENT ARRIVAL' (the earlier SETA/SETB was a misread), corroborated by p133's ORA1 conductor from CON1-22/23 and p127. Matches PLC X003 ORA1. Field-verify polarity before commissioning</t>
         </is>
       </c>
     </row>
@@ -34106,17 +34106,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN6-27</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">SER</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN6-27</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -34126,7 +34126,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESOLVED 2026-08-11 (owner decision AG): CN6-27 = wire mnemonic SER, function SERVO ERROR - the SINGLE combined servo-alarm contact for all three axes (only one SER entry on the 50-pin CN6; docs/servo_amp_analysis.md 3.3 confirms SERVO ALARM lands at the terminal unit's CN6). Consolidated to one 7i84U-A input (IN10) that fans out to all three joint amp-faults; the former per-axis X/Y/Z_DRIVE_FAULT (IN10/11/12) design is retired and IN11/IN12 are freed to spare</t>
+          <t xml:space="preserve">RETRACTED 2026-09-02 (owner approved): p85 reads CN6-27 = SFR SPINDLE FORWARD (between CN6-26 ZS1 and CN6-28 SRV); no SER pin exists on CN6, and docs/photo_survey_misc.md's independent read of the same sheet agrees. The 2026-08-11 combined-SER consolidation rests on a misread. IN10 stays reserved for a combined servo alarm; re-derive the source, most likely at the HD81/HD101 amp ALM contacts directly. The one-input-fans-to-three-joints design intent stands; the former per-axis X/Y/Z_DRIVE_FAULT (IN10/11/12) design remains retired and IN11/IN12 are freed to spare</t>
         </is>
       </c>
     </row>
@@ -34983,17 +34983,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">232</t>
+          <t xml:space="preserve">-LZ2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2nd-S LEVEL</t>
+          <t xml:space="preserve">2nd -Z OVER TRAVEL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">coolant lvl</t>
+          <t xml:space="preserve">limit</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -35025,7 +35025,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">233</t>
+          <t xml:space="preserve">355</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -35366,22 +35366,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE TIMER</t>
+          <t xml:space="preserve">WAY LUBE WARNING TIMER</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">lube</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNQ-36</t>
+          <t xml:space="preserve">CN3-36</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-W</t>
+          <t xml:space="preserve">CA4-V</t>
         </is>
       </c>
     </row>
@@ -35408,22 +35408,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE FWD/REV SHIFTER</t>
+          <t xml:space="preserve">MACHINE POWER SUPPLY (X78 MPWS.M; fed by PS-1 hydraulic pressure switch per p133)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">safety</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNQ-37</t>
+          <t xml:space="preserve">CND4-47</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-V</t>
+          <t xml:space="preserve">CA4-W</t>
         </is>
       </c>
     </row>
@@ -35492,7 +35492,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 1</t>
+          <t xml:space="preserve">MANUAL MAGAZINE ROTATE PB (X07 TSPB.M)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -35534,7 +35534,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 2</t>
+          <t xml:space="preserve">MAGAZINE POSITION 1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -35576,7 +35576,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 4</t>
+          <t xml:space="preserve">MAGAZINE POSITION 2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -35618,7 +35618,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 8</t>
+          <t xml:space="preserve">MAGAZINE POSITION 4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -35660,7 +35660,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 10</t>
+          <t xml:space="preserve">MAGAZINE POSITION 8</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -35702,7 +35702,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE POSITION OK</t>
+          <t xml:space="preserve">MAGAZINE POSITION 10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -35739,12 +35739,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">218</t>
+          <t xml:space="preserve">213</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE POWER OPEN</t>
+          <t xml:space="preserve">MAGAZINE INPOSITION (MIPRS PRS-13)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -35907,12 +35907,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">+LTZ</t>
+          <t xml:space="preserve">+LY2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z-AXIS OVER TRAVEL</t>
+          <t xml:space="preserve">2nd +Y OVER TRAVEL (PRS-55; to relay 1237/PYOT)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -35922,12 +35922,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-12</t>
+          <t xml:space="preserve">1-12</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-L</t>
+          <t xml:space="preserve">CA4-e</t>
         </is>
       </c>
     </row>
@@ -36206,7 +36206,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOOL MEASURE DEVICE TIMER</t>
+          <t xml:space="preserve">TOOL MEASURING ARM EXTEND</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -36243,12 +36243,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">345</t>
+          <t xml:space="preserve">343</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOOL MEASURE DEVICE SW</t>
+          <t xml:space="preserve">TOOL MEASURING ARM RETRACT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -36285,17 +36285,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">362</t>
+          <t xml:space="preserve">238</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE LUBE TIMER</t>
+          <t xml:space="preserve">TOOL LENGTH MEASURE DEC.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">lube</t>
+          <t xml:space="preserve">probe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -36332,12 +36332,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE LUBE PRESS SW</t>
+          <t xml:space="preserve">TOOL MEASURE SKIP</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">lube</t>
+          <t xml:space="preserve">probe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -36369,7 +36369,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">238</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -36389,7 +36389,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-N</t>
+          <t xml:space="preserve">CA4-U</t>
         </is>
       </c>
     </row>
@@ -36416,12 +36416,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPARE INPUT 2</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK 2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">spare</t>
+          <t xml:space="preserve">safety</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">EHB</t>
+          <t xml:space="preserve">EMB</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -36468,7 +36468,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN5-44</t>
+          <t xml:space="preserve">CN5-4</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -36510,7 +36510,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CN5-5</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -36542,7 +36542,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE TOOL CLAMP OK</t>
+          <t xml:space="preserve">SPINDLE TOOL DETECTOR</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -36579,22 +36579,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">524</t>
+          <t xml:space="preserve">G24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC24V SELECTOR (X Y Z 4 5 6)</t>
+          <t xml:space="preserve">DC24V -COM (ELECTRICAL CAB)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">selector</t>
+          <t xml:space="preserve">common</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-5</t>
+          <t xml:space="preserve">CN5-8</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -36663,17 +36663,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">CP24</t>
+          <t xml:space="preserve">CH24</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEED HOLD SW (LATCH)</t>
+          <t xml:space="preserve">HEAD LUBE PRESS ALARM</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">operator</t>
+          <t xml:space="preserve">lube</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -36683,7 +36683,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-H</t>
+          <t xml:space="preserve">CA4-j</t>
         </is>
       </c>
     </row>
@@ -36873,12 +36873,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">EHB</t>
+          <t xml:space="preserve">*ESP</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMERGENCY STOP</t>
+          <t xml:space="preserve">EMERGENCY STOP (chain status to NC X000)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -36888,7 +36888,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN5-43</t>
+          <t xml:space="preserve">CND1-3</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -36915,12 +36915,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">141</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEAD LUBE PRESSURE</t>
+          <t xml:space="preserve">HEAD LUBE PRESSURE ALARM</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -36930,7 +36930,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-28</t>
+          <t xml:space="preserve">4-48</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -37056,7 +37056,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN6-51</t>
+          <t xml:space="preserve">CN4-6</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -37098,7 +37098,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN6-8</t>
+          <t xml:space="preserve">CN4-8</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -37140,7 +37140,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN6-7</t>
+          <t xml:space="preserve">CN4-7</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -37182,7 +37182,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN6-9</t>
+          <t xml:space="preserve">CN4-9</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -37224,7 +37224,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN6-10</t>
+          <t xml:space="preserve">CN4-10</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -37298,7 +37298,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORIENT LOOP CHECK</t>
+          <t xml:space="preserve">LOW GEAR SHIFT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -37308,7 +37308,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-13</t>
+          <t xml:space="preserve">CN4-13</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -37550,12 +37550,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">OIL TEMP DETECTOR</t>
+          <t xml:space="preserve">TOOL DETECTOR (MGTDPRS X05)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">alarm</t>
+          <t xml:space="preserve">ATC</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -37565,7 +37565,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-0503</t>
+          <t xml:space="preserve">TB503-b11</t>
         </is>
       </c>
     </row>
@@ -37760,22 +37760,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE TIMER</t>
+          <t xml:space="preserve">SPINDLE TOOL DETECTOR (SPTDPRS X5B)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">spindle</t>
+          <t xml:space="preserve">ATC</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-44</t>
+          <t xml:space="preserve">4-26</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D1 1-14</t>
+          <t xml:space="preserve">TB504-0101</t>
         </is>
       </c>
     </row>
@@ -37881,7 +37881,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">ZS1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -37901,7 +37901,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON 4-3</t>
+          <t xml:space="preserve">CON1-3</t>
         </is>
       </c>
     </row>
@@ -37923,7 +37923,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS2</t>
+          <t xml:space="preserve">ZS2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -37970,7 +37970,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE REV ROLLER THERMAL</t>
+          <t xml:space="preserve">SPINDLE CONTROLLER NORMAL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -38427,12 +38427,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">SETA</t>
+          <t xml:space="preserve">ORA1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">set A</t>
+          <t xml:space="preserve">SPINDLE ORIENT ARRIVAL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -38469,12 +38469,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">SETB</t>
+          <t xml:space="preserve">ORA2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">set B</t>
+          <t xml:space="preserve">SPINDLE ORIENT ARRIVAL (2)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -38516,7 +38516,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXTERNAL TRIP PROTECTOR</t>
+          <t xml:space="preserve">THERMAL TRIP PROTECTOR</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -38526,12 +38526,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN23-14</t>
+          <t xml:space="preserve">CND4-46</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB1-31</t>
+          <t xml:space="preserve">TB1-144</t>
         </is>
       </c>
     </row>
@@ -38600,7 +38600,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">OVER RUN EMG STOP</t>
+          <t xml:space="preserve">MAIN TRANSF. OVER HEAT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -38610,7 +38610,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-30</t>
+          <t xml:space="preserve">4-50</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -38694,7 +38694,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN5-5</t>
+          <t xml:space="preserve">CN2-41</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -38988,7 +38988,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-44</t>
+          <t xml:space="preserve">CND2-7</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -39015,27 +39015,27 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISP1</t>
+          <t xml:space="preserve">DINTCSS</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-AXIS LINC INTERLOCK CANCEL</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK CANCEL (SS-51 selector; X1D)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4th axis</t>
+          <t xml:space="preserve">safety</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-37</t>
+          <t xml:space="preserve">1-37</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB1-33</t>
+          <t xml:space="preserve">TB1-151</t>
         </is>
       </c>
     </row>
@@ -39057,22 +39057,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">XYZR4</t>
+          <t xml:space="preserve">*DEC4</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-AXIS UNCLAMP INTERLOCK CANCEL</t>
+          <t xml:space="preserve">4 AXIS ZERO RETURN DEC.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4th axis</t>
+          <t xml:space="preserve">homing</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-14</t>
+          <t xml:space="preserve">4-44</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -39104,7 +39104,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-AXIS LIMIT OVER-TRAVEL RELEASE</t>
+          <t xml:space="preserve">INDEX TABLE TYPE 4-AXIS UNCLAMPED (LS)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -39141,17 +39141,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1NRAILS</t>
+          <t xml:space="preserve">INHRLS</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE REAR L.S.</t>
+          <t xml:space="preserve">INHIBIT READ LS</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">NC iface</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -39161,7 +39161,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">-1NRAILS</t>
+          <t xml:space="preserve">-INHRLS</t>
         </is>
       </c>
     </row>
@@ -39356,22 +39356,22 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYCLE FINISH</t>
+          <t xml:space="preserve">PATO LIGHT (patrol light)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">NC iface</t>
+          <t xml:space="preserve">aux</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-16</t>
+          <t xml:space="preserve">CND23-29</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">CV-29</t>
+          <t xml:space="preserve">CN301A-1</t>
         </is>
       </c>
     </row>
@@ -39393,22 +39393,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYFIN</t>
+          <t xml:space="preserve">M44T</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYCLE FINISH (2)</t>
+          <t xml:space="preserve">mag M44T</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">NC iface</t>
+          <t xml:space="preserve">ATC</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-29</t>
+          <t xml:space="preserve">3-48</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -39435,7 +39435,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">MA3T</t>
+          <t xml:space="preserve">M43T</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -39450,7 +39450,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-48</t>
+          <t xml:space="preserve">3-49</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -39477,7 +39477,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">MA3T</t>
+          <t xml:space="preserve">M45T</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -39492,7 +39492,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-49</t>
+          <t xml:space="preserve">3-45</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -39519,22 +39519,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">MA3T</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag M45T</t>
+          <t xml:space="preserve">(not used - blank on source table)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">spare</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-45</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -39692,7 +39692,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOW GEAR OVER TRAVEL</t>
+          <t xml:space="preserve">LOW GEAR SELECT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -39771,12 +39771,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">+LYZ</t>
+          <t xml:space="preserve">+LY2</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">+YZ OVER TRAVEL</t>
+          <t xml:space="preserve">+Y 2nd OVER TRAVEL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -39813,12 +39813,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">-LYZ</t>
+          <t xml:space="preserve">-LZ2</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">-YZ OVER TRAVEL</t>
+          <t xml:space="preserve">-Z 2nd OVER TRAVEL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -40028,17 +40028,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAIN PANE POWER ON</t>
+          <t xml:space="preserve">DC24V +COM (MACHINE)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">power</t>
+          <t xml:space="preserve">common</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN12-21</t>
+          <t xml:space="preserve">CN2-21</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -40065,7 +40065,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">238</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -40107,22 +40107,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">241</t>
+          <t xml:space="preserve">340</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">POWER ON MAIN LAMP INTERLOCK</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK 2</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">power</t>
+          <t xml:space="preserve">safety</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-23</t>
+          <t xml:space="preserve">CN2-39</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -40149,22 +40149,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">main lamp interlock 2</t>
+          <t xml:space="preserve">(not used - blank on source table)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">power</t>
+          <t xml:space="preserve">spare</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">-39</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -40191,12 +40191,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">ES1</t>
+          <t xml:space="preserve">ZS1</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE SPEED</t>
+          <t xml:space="preserve">SPINDLE ZERO SPEED</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -40206,7 +40206,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-1</t>
+          <t xml:space="preserve">CN4-1</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -40233,22 +40233,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">SER</t>
+          <t xml:space="preserve">SFR</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVO ERROR</t>
+          <t xml:space="preserve">SPINDLE FORWARD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">servo</t>
+          <t xml:space="preserve">spindle</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN2-13</t>
+          <t xml:space="preserve">3-14</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -40280,7 +40280,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE SERVO</t>
+          <t xml:space="preserve">SPINDLE REVERSE</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -40322,7 +40322,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE READY</t>
+          <t xml:space="preserve">SPINDLE RUN</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -40364,7 +40364,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUN COMMAND</t>
+          <t xml:space="preserve">ORIENT COMMAND</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">T-CODE NO MEMORY</t>
+          <t xml:space="preserve">TOOL CHANGE MEMORY</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -40416,7 +40416,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN12-1</t>
+          <t xml:space="preserve">CND23-49</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -40443,12 +40443,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">NSFT</t>
+          <t xml:space="preserve">NSPT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">NG TOOL</t>
+          <t xml:space="preserve">NO SPARE TOOL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -40490,7 +40490,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE OIL TOOL DETECTOR</t>
+          <t xml:space="preserve">MAGAZINE TOOL DETECTOR</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -40532,7 +40532,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE HEAD LUBE PRESSURE</t>
+          <t xml:space="preserve">HEAD LUBE PRESSURE</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -40542,7 +40542,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN11-6</t>
+          <t xml:space="preserve">CN1-6</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -40826,7 +40826,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE SPINDLE TOOL DETECTOR</t>
+          <t xml:space="preserve">SPINDLE TOOL DETECTOR</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -40836,7 +40836,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN12-42</t>
+          <t xml:space="preserve">CN2-42</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -40863,7 +40863,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">208B</t>
+          <t xml:space="preserve">708B</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -40905,7 +40905,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">208A</t>
+          <t xml:space="preserve">708A</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -41031,7 +41031,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">213</t>
+          <t xml:space="preserve">713</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -41073,7 +41073,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">215</t>
+          <t xml:space="preserve">715</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -41115,7 +41115,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">216</t>
+          <t xml:space="preserve">716</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -41157,7 +41157,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">217</t>
+          <t xml:space="preserve">717</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -41199,7 +41199,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">262</t>
+          <t xml:space="preserve">762</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -41241,7 +41241,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">261</t>
+          <t xml:space="preserve">761</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -41283,7 +41283,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">735</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -41325,7 +41325,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">236</t>
+          <t xml:space="preserve">736</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -41367,7 +41367,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">731</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -41409,7 +41409,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">227</t>
+          <t xml:space="preserve">727</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -41451,12 +41451,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">236</t>
+          <t xml:space="preserve">736</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLOOD COOLANT MOTOR STARTER</t>
+          <t xml:space="preserve">FLOOD COOLANT MOTOR STARTER (p85 reads 736; p140/p78 read 836 - jacket read decides)</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -41493,7 +41493,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">835</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -51963,7 +51963,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">probe-in</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -51978,7 +51978,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESERVED</t>
+          <t xml:space="preserve">PROPOSED</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -52894,7 +52894,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE TIMER</t>
+          <t xml:space="preserve">WAY LUBE WARNING TIMER</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -52909,7 +52909,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE TIMER</t>
+          <t xml:space="preserve">WAY LUBE WARNING TIMER</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -52919,7 +52919,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">lube</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -52946,7 +52946,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE FWD/REV SHIFTER</t>
+          <t xml:space="preserve">MACHINE POWER SUPPLY (X78 MPWS.M; fed by PS-1 hydraulic pressure switch per p133)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -52961,7 +52961,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE FWD/REV SHIFTER</t>
+          <t xml:space="preserve">MACHINE POWER SUPPLY (X78 MPWS.M; fed by PS-1 hydraulic pressure switch per p133)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -52971,7 +52971,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">safety</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -53045,17 +53045,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB2 IN19</t>
+          <t xml:space="preserve">none none</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 1</t>
+          <t xml:space="preserve">MANUAL MAGAZINE ROTATE PB (X07 TSPB.M)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag-bcd-bit0</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -53065,12 +53065,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAG_BCD_BIT0</t>
+          <t xml:space="preserve">MANUAL MAGAZINE ROTATE PB (X07 TSPB.M)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -53097,17 +53097,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB2 IN20</t>
+          <t xml:space="preserve">TB2 IN19</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 2</t>
+          <t xml:space="preserve">MAGAZINE POSITION 1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag-bcd-bit1</t>
+          <t xml:space="preserve">mag-bcd-bit0</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -53117,7 +53117,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAG_BCD_BIT1</t>
+          <t xml:space="preserve">MAG_BCD_BIT0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -53149,17 +53149,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB2 IN21</t>
+          <t xml:space="preserve">TB2 IN20</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 4</t>
+          <t xml:space="preserve">MAGAZINE POSITION 2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag-bcd-bit2</t>
+          <t xml:space="preserve">mag-bcd-bit1</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -53169,7 +53169,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAG_BCD_BIT2</t>
+          <t xml:space="preserve">MAG_BCD_BIT1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -53201,17 +53201,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB2 IN22</t>
+          <t xml:space="preserve">TB2 IN21</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 8</t>
+          <t xml:space="preserve">MAGAZINE POSITION 4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag-bcd-bit3</t>
+          <t xml:space="preserve">mag-bcd-bit2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -53221,7 +53221,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAG_BCD_BIT3</t>
+          <t xml:space="preserve">MAG_BCD_BIT2</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -53253,17 +53253,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB2 IN23</t>
+          <t xml:space="preserve">TB2 IN22</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE ROT POS 10</t>
+          <t xml:space="preserve">MAGAZINE POSITION 8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag-bcd-bit4</t>
+          <t xml:space="preserve">mag-bcd-bit3</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -53273,7 +53273,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAG_BCD_BIT4</t>
+          <t xml:space="preserve">MAG_BCD_BIT3</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -53305,17 +53305,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB2 IN28</t>
+          <t xml:space="preserve">TB2 IN23</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE POSITION OK</t>
+          <t xml:space="preserve">MAGAZINE POSITION 10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag-in-pos</t>
+          <t xml:space="preserve">mag-bcd-bit4</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -53325,7 +53325,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAG_IN_POS</t>
+          <t xml:space="preserve">MAG_BCD_BIT4</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -53357,32 +53357,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">none none</t>
+          <t xml:space="preserve">TB2 IN28</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE POWER OPEN</t>
+          <t xml:space="preserve">MAGAZINE INPOSITION (MIPRS PRS-13)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">mag-in-pos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">218</t>
+          <t xml:space="preserve">213</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE POWER OPEN</t>
+          <t xml:space="preserve">MAG_IN_POS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNALLOCATED</t>
+          <t xml:space="preserve">FACTORY_INTERFACE</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -53570,7 +53570,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z-AXIS OVER TRAVEL</t>
+          <t xml:space="preserve">2nd +Y OVER TRAVEL (PRS-55; to relay 1237/PYOT)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -53580,12 +53580,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">+LTZ</t>
+          <t xml:space="preserve">+LY2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z-AXIS OVER TRAVEL</t>
+          <t xml:space="preserve">2nd +Y OVER TRAVEL (PRS-55; to relay 1237/PYOT)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -54610,7 +54610,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOOL MEASURE DEVICE TIMER</t>
+          <t xml:space="preserve">TOOL MEASURING ARM EXTEND</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -54625,7 +54625,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOOL MEASURE DEVICE TIMER</t>
+          <t xml:space="preserve">TOOL MEASURING ARM EXTEND</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -54662,7 +54662,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOOL MEASURE DEVICE SW</t>
+          <t xml:space="preserve">TOOL MEASURING ARM RETRACT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -54672,12 +54672,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">345</t>
+          <t xml:space="preserve">343</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOOL MEASURE DEVICE SW</t>
+          <t xml:space="preserve">TOOL MEASURING ARM RETRACT</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -54714,7 +54714,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE LUBE TIMER</t>
+          <t xml:space="preserve">TOOL LENGTH MEASURE DEC.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -54724,12 +54724,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">362</t>
+          <t xml:space="preserve">238</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE LUBE TIMER</t>
+          <t xml:space="preserve">TOOL LENGTH MEASURE DEC.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -54739,7 +54739,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">lube</t>
+          <t xml:space="preserve">probe</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -54766,7 +54766,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE LUBE PRESS SW</t>
+          <t xml:space="preserve">TOOL MEASURE SKIP</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -54781,7 +54781,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE LUBE PRESS SW</t>
+          <t xml:space="preserve">TOOL MEASURE SKIP</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -54791,7 +54791,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">lube</t>
+          <t xml:space="preserve">probe</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -54813,7 +54813,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB2 IN24</t>
+          <t xml:space="preserve">none none</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -54823,22 +54823,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">door-interlock</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">238</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOOR_INTERLOCK</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -54870,7 +54870,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPARE INPUT 2</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK 2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -54885,7 +54885,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPARE INPUT 2</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK 2</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -54895,7 +54895,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">spare</t>
+          <t xml:space="preserve">safety</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -54932,7 +54932,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">EHB</t>
+          <t xml:space="preserve">EMB</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -55026,7 +55026,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE TOOL CLAMP OK</t>
+          <t xml:space="preserve">SPINDLE TOOL DETECTOR</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -55041,7 +55041,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE TOOL CLAMP OK</t>
+          <t xml:space="preserve">SPINDLE TOOL DETECTOR</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -55078,7 +55078,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC24V SELECTOR (X Y Z 4 5 6)</t>
+          <t xml:space="preserve">DC24V -COM (ELECTRICAL CAB)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -55088,12 +55088,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">524</t>
+          <t xml:space="preserve">G24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC24V SELECTOR (X Y Z 4 5 6)</t>
+          <t xml:space="preserve">DC24V -COM (ELECTRICAL CAB)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -55103,7 +55103,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">selector</t>
+          <t xml:space="preserve">common</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -55182,7 +55182,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEED HOLD SW (LATCH)</t>
+          <t xml:space="preserve">HEAD LUBE PRESS ALARM</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -55192,12 +55192,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">CP24</t>
+          <t xml:space="preserve">CH24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEED HOLD SW (LATCH)</t>
+          <t xml:space="preserve">HEAD LUBE PRESS ALARM</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -55207,7 +55207,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">operator</t>
+          <t xml:space="preserve">lube</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -55697,37 +55697,37 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB2 IN26</t>
+          <t xml:space="preserve">none none</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2nd-S LEVEL</t>
+          <t xml:space="preserve">2nd -Z OVER TRAVEL</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">coolant-low</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">232</t>
+          <t xml:space="preserve">-LZ2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">COOLANT_LOW</t>
+          <t xml:space="preserve">2nd -Z OVER TRAVEL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">coolant lvl</t>
+          <t xml:space="preserve">limit</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -55764,7 +55764,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">233</t>
+          <t xml:space="preserve">355</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -56534,7 +56534,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXTERNAL TRIP PROTECTOR</t>
+          <t xml:space="preserve">THERMAL TRIP PROTECTOR</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -56638,7 +56638,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">OVER RUN EMG STOP</t>
+          <t xml:space="preserve">MAIN TRANSF. OVER HEAT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -56653,7 +56653,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">OVER RUN EMG STOP</t>
+          <t xml:space="preserve">MAIN TRANSF. OVER HEAT</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -57158,7 +57158,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-AXIS LINC INTERLOCK CANCEL</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK CANCEL (SS-51 selector; X1D)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -57168,12 +57168,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISP1</t>
+          <t xml:space="preserve">DINTCSS</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-AXIS LINC INTERLOCK CANCEL</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK CANCEL (SS-51 selector; X1D)</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -57183,7 +57183,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4th axis</t>
+          <t xml:space="preserve">safety</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -57210,7 +57210,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-AXIS UNCLAMP INTERLOCK CANCEL</t>
+          <t xml:space="preserve">4 AXIS ZERO RETURN DEC.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -57220,12 +57220,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">XYZR4</t>
+          <t xml:space="preserve">*DEC4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-AXIS UNCLAMP INTERLOCK CANCEL</t>
+          <t xml:space="preserve">4 AXIS ZERO RETURN DEC.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -57235,7 +57235,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4th axis</t>
+          <t xml:space="preserve">homing</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -57262,7 +57262,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-AXIS LIMIT OVER-TRAVEL RELEASE</t>
+          <t xml:space="preserve">INDEX TABLE TYPE 4-AXIS UNCLAMPED (LS)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -57277,7 +57277,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-AXIS LIMIT OVER-TRAVEL RELEASE</t>
+          <t xml:space="preserve">INDEX TABLE TYPE 4-AXIS UNCLAMPED (LS)</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -57314,7 +57314,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE REAR L.S.</t>
+          <t xml:space="preserve">INHIBIT READ LS</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -57324,12 +57324,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1NRAILS</t>
+          <t xml:space="preserve">INHRLS</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE REAR L.S.</t>
+          <t xml:space="preserve">INHIBIT READ LS</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -57339,7 +57339,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">NC iface</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -57574,7 +57574,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYCLE FINISH</t>
+          <t xml:space="preserve">PATO LIGHT (patrol light)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -57589,7 +57589,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYCLE FINISH</t>
+          <t xml:space="preserve">PATO LIGHT (patrol light)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -57599,7 +57599,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">NC iface</t>
+          <t xml:space="preserve">aux</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -57626,7 +57626,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYCLE FINISH (2)</t>
+          <t xml:space="preserve">mag M44T</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -57636,12 +57636,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYFIN</t>
+          <t xml:space="preserve">M44T</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYCLE FINISH (2)</t>
+          <t xml:space="preserve">mag M44T</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -57651,7 +57651,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">NC iface</t>
+          <t xml:space="preserve">ATC</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -57688,7 +57688,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">MA3T</t>
+          <t xml:space="preserve">M43T</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -57740,7 +57740,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">MA3T</t>
+          <t xml:space="preserve">M45T</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -57782,7 +57782,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag M45T</t>
+          <t xml:space="preserve">(not used - blank on source table)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -57792,12 +57792,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">MA3T</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">mag M45T</t>
+          <t xml:space="preserve">(not used - blank on source table)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -57807,7 +57807,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">spare</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -58042,7 +58042,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOW GEAR OVER TRAVEL</t>
+          <t xml:space="preserve">LOW GEAR SELECT</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -58057,7 +58057,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOW GEAR OVER TRAVEL</t>
+          <t xml:space="preserve">LOW GEAR SELECT</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -58146,7 +58146,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">+YZ OVER TRAVEL</t>
+          <t xml:space="preserve">+Y 2nd OVER TRAVEL</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -58156,12 +58156,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">+LYZ</t>
+          <t xml:space="preserve">+LY2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">+YZ OVER TRAVEL</t>
+          <t xml:space="preserve">+Y 2nd OVER TRAVEL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -58198,7 +58198,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-YZ OVER TRAVEL</t>
+          <t xml:space="preserve">-Z 2nd OVER TRAVEL</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -58208,12 +58208,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-LYZ</t>
+          <t xml:space="preserve">-LZ2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-YZ OVER TRAVEL</t>
+          <t xml:space="preserve">-Z 2nd OVER TRAVEL</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -58614,7 +58614,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAIN PANE POWER ON</t>
+          <t xml:space="preserve">DC24V +COM (MACHINE)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -58629,7 +58629,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAIN PANE POWER ON</t>
+          <t xml:space="preserve">DC24V +COM (MACHINE)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -58639,7 +58639,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">power</t>
+          <t xml:space="preserve">common</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -58728,7 +58728,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">238</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -58770,7 +58770,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">POWER ON MAIN LAMP INTERLOCK</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK 2</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -58780,12 +58780,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">241</t>
+          <t xml:space="preserve">340</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">POWER ON MAIN LAMP INTERLOCK</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK 2</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -58795,7 +58795,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">power</t>
+          <t xml:space="preserve">safety</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -58822,7 +58822,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">main lamp interlock 2</t>
+          <t xml:space="preserve">(not used - blank on source table)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -58832,12 +58832,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">main lamp interlock 2</t>
+          <t xml:space="preserve">(not used - blank on source table)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -58847,7 +58847,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">power</t>
+          <t xml:space="preserve">spare</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -58874,7 +58874,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE SPEED</t>
+          <t xml:space="preserve">SPINDLE ZERO SPEED</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -58884,12 +58884,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">ES1</t>
+          <t xml:space="preserve">ZS1</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE SPEED</t>
+          <t xml:space="preserve">SPINDLE ZERO SPEED</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -58921,37 +58921,37 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB3 IN10</t>
+          <t xml:space="preserve">none none</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVO ERROR</t>
+          <t xml:space="preserve">SPINDLE FORWARD</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">servo-fault</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">SER</t>
+          <t xml:space="preserve">SFR</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVO_FAULT</t>
+          <t xml:space="preserve">SPINDLE FORWARD</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">servo</t>
+          <t xml:space="preserve">spindle</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -58978,7 +58978,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE SERVO</t>
+          <t xml:space="preserve">SPINDLE REVERSE</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -58993,7 +58993,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE SERVO</t>
+          <t xml:space="preserve">SPINDLE REVERSE</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -59030,7 +59030,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE READY</t>
+          <t xml:space="preserve">SPINDLE RUN</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -59045,7 +59045,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE READY</t>
+          <t xml:space="preserve">SPINDLE RUN</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -59082,7 +59082,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUN COMMAND</t>
+          <t xml:space="preserve">ORIENT COMMAND</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -59097,7 +59097,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUN COMMAND</t>
+          <t xml:space="preserve">ORIENT COMMAND</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -59238,7 +59238,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">T-CODE NO MEMORY</t>
+          <t xml:space="preserve">TOOL CHANGE MEMORY</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -59253,7 +59253,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">T-CODE NO MEMORY</t>
+          <t xml:space="preserve">TOOL CHANGE MEMORY</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -59290,7 +59290,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">NG TOOL</t>
+          <t xml:space="preserve">NO SPARE TOOL</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -59300,12 +59300,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">NSFT</t>
+          <t xml:space="preserve">NSPT</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">NG TOOL</t>
+          <t xml:space="preserve">NO SPARE TOOL</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -59446,7 +59446,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE OIL TOOL DETECTOR</t>
+          <t xml:space="preserve">MAGAZINE TOOL DETECTOR</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -59461,7 +59461,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE OIL TOOL DETECTOR</t>
+          <t xml:space="preserve">MAGAZINE TOOL DETECTOR</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -59550,7 +59550,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE HEAD LUBE PRESSURE</t>
+          <t xml:space="preserve">HEAD LUBE PRESSURE</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -60122,7 +60122,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE SPINDLE TOOL DETECTOR</t>
+          <t xml:space="preserve">SPINDLE TOOL DETECTOR</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -60174,7 +60174,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMERGENCY STOP</t>
+          <t xml:space="preserve">EMERGENCY STOP (chain status to NC X000)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -60184,12 +60184,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">EHB</t>
+          <t xml:space="preserve">*ESP</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMERGENCY STOP</t>
+          <t xml:space="preserve">EMERGENCY STOP (chain status to NC X000)</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -60226,7 +60226,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEAD LUBE PRESSURE</t>
+          <t xml:space="preserve">HEAD LUBE PRESSURE ALARM</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -60236,12 +60236,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">141</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEAD LUBE PRESSURE</t>
+          <t xml:space="preserve">HEAD LUBE PRESSURE ALARM</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -60902,7 +60902,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORIENT LOOP CHECK</t>
+          <t xml:space="preserve">LOW GEAR SHIFT</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -62145,17 +62145,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB3 IN1</t>
+          <t xml:space="preserve">none none</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">OIL TEMP DETECTOR</t>
+          <t xml:space="preserve">TOOL DETECTOR (MGTDPRS X05)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">atc-z-zone</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -62165,17 +62165,17 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC_ZONE_Z</t>
+          <t xml:space="preserve">TOOL DETECTOR (MGTDPRS X05)</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">alarm</t>
+          <t xml:space="preserve">ATC</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -62405,17 +62405,17 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB3 IN0</t>
+          <t xml:space="preserve">none none</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE TIMER</t>
+          <t xml:space="preserve">SPINDLE TOOL DETECTOR (SPTDPRS X5B)</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">atc-y-zone</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -62425,17 +62425,17 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC_ZONE_Y</t>
+          <t xml:space="preserve">SPINDLE TOOL DETECTOR (SPTDPRS X5B)</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">spindle</t>
+          <t xml:space="preserve">ATC</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -62784,7 +62784,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">208B</t>
+          <t xml:space="preserve">708B</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -62836,7 +62836,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">208A</t>
+          <t xml:space="preserve">708A</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -62992,7 +62992,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">213</t>
+          <t xml:space="preserve">713</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -63044,7 +63044,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">215</t>
+          <t xml:space="preserve">715</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -63096,7 +63096,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">216</t>
+          <t xml:space="preserve">716</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -63148,7 +63148,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">217</t>
+          <t xml:space="preserve">717</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -63200,7 +63200,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">262</t>
+          <t xml:space="preserve">762</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -63252,7 +63252,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">261</t>
+          <t xml:space="preserve">761</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -63304,7 +63304,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">735</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -63356,7 +63356,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">236</t>
+          <t xml:space="preserve">736</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -63408,7 +63408,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">731</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -63460,7 +63460,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">227</t>
+          <t xml:space="preserve">727</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -63497,32 +63497,32 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB2 OUT11</t>
+          <t xml:space="preserve">none none</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLOOD COOLANT MOTOR STARTER</t>
+          <t xml:space="preserve">FLOOD COOLANT MOTOR STARTER (p85 reads 736; p140/p78 read 836 - jacket read decides)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">flood-coolant</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">236</t>
+          <t xml:space="preserve">736</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">COOLANT_ON</t>
+          <t xml:space="preserve">FLOOD COOLANT MOTOR STARTER (p85 reads 736; p140/p78 read 836 - jacket read decides)</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -63564,7 +63564,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">835</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -64864,7 +64864,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">ZS1</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -64916,7 +64916,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS2</t>
+          <t xml:space="preserve">ZS2</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -64958,7 +64958,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE REV ROLLER THERMAL</t>
+          <t xml:space="preserve">SPINDLE CONTROLLER NORMAL</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -65629,32 +65629,32 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB3 IN4</t>
+          <t xml:space="preserve">none none</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">set A</t>
+          <t xml:space="preserve">SPINDLE ORIENT ARRIVAL</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">spindle-oriented</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">SETA</t>
+          <t xml:space="preserve">ORA1</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE_ORIENT_ARRIVAL</t>
+          <t xml:space="preserve">SPINDLE ORIENT ARRIVAL</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">FACTORY_INTERFACE</t>
+          <t xml:space="preserve">UNALLOCATED</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -65686,7 +65686,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">set B</t>
+          <t xml:space="preserve">SPINDLE ORIENT ARRIVAL (2)</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -65696,12 +65696,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">SETB</t>
+          <t xml:space="preserve">ORA2</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">set B</t>
+          <t xml:space="preserve">SPINDLE ORIENT ARRIVAL (2)</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -70541,7 +70541,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -70573,7 +70573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -70605,7 +70605,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -70637,7 +70637,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -70701,7 +70701,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -70733,7 +70733,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">

--- a/wiring/MESAC_Wiring_Crosswalk.xlsx
+++ b/wiring/MESAC_Wiring_Crosswalk.xlsx
@@ -144,7 +144,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">DOOR_INTERLOCK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5596,42 +5596,42 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">OEM_SAFETY_RETAIN</t>
+          <t xml:space="preserve">MESA_ROUTE</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">7i84U-A</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">TB2</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">IN24</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">door-interlock</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNALLOCATED</t>
+          <t xml:space="preserve">FACTORY_INTERFACE</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t xml:space="preserve">OEM_SAFETY_RETAIN</t>
+          <t xml:space="preserve">ROUTE_DEFINED_FIELD_VERIFY</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retain in the untouched OEM safety circuit; no Mesa GPIO route.</t>
+          <t xml:space="preserve">Series-wired 2026-08-03: X01D ITMDSS consolidated with LS-140/141 pair. Choose door-open versus door-closed net after normal state is measured. | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/estop_ladder_transcription.md] | [2026-09-02 AUDIT (owner approved): factory wire corrected 238 -&gt; 341 per dwg 4143075321 p84 (CN2-38 = 341 MACHINE DOOR INTERLOCK, corroborated by CN6-23 = 341 on p85 at 400 DPI); wire 238 is CN2-36 TOOL LENGTH MEASURE DEC. Companion CN2-39/CN6-24 = 340 door interlock 2.]</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COOLANT_ON</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -20960,42 +20960,42 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">MESA_ROUTE</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">7i84U-A</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">TB2</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">OUT11</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">flood-coolant</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNALLOCATED</t>
+          <t xml:space="preserve">FACTORY_INTERFACE</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">HOLD_OEM_CONFLICT</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t xml:space="preserve">No current Mesa authority row claims this conductor; review only if the OEM function is retained.</t>
+          <t xml:space="preserve">Authority wire  conflicts with terminal-unit table wire 736. Continuity trace required before landing.</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
@@ -24692,7 +24692,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SPINDLE_ORIENT_ARRIVAL</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -24732,42 +24732,42 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">MESA_ROUTE</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">7i84U-A</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">TB3</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">IN4</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">spindle-oriented</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNALLOCATED</t>
+          <t xml:space="preserve">FACTORY_INTERFACE</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_MESA_ALLOCATION</t>
+          <t xml:space="preserve">ROUTE_DEFINED_FIELD_VERIFY</t>
         </is>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t xml:space="preserve">No current Mesa authority row claims this conductor; review only if the OEM function is retained.</t>
+          <t xml:space="preserve">ATC cannot cycle without orient; confirm FR-SX terminal and polarity | [RECON 2026-08-08 §A: element list confirms X003 ORA1 'ORIENT ARRIVAL' (ladder 3006/4810/5509) on 060231] | [RECON 2026-08-08 §D: FR-SX OBA1(t22)/OBA2(t23) -&gt; CN4-16/CN4-17 (digits verify)] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/spindle_run_ladder_transcription.md] | [2026-09-02 AUDIT (owner approved): factory wire corrected SETA -&gt; ORA1 per dwg 4143075321 p84 at 560 DPI (CN4-16 = ORA1 "SPINDLE ORIENT ARRIVAL"), corroborated by dwg 4143075403 p127 (CON1-22/23 OBA1/OBA2 -&gt; CN4-16/-17). "SETA/set A" was a misread; CN4-17 = ORA2. Resolves this row's earlier LOW CONFIDENCE flag in the ladder's favor.]</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -30413,7 +30413,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7i49man.pdf printed pp5 and 12; docs/grounding_shielding_plan.md</t>
+          <t xml:space="preserve">7i49man.pdf printed pp5 and 9; docs/grounding_shielding_plan.md</t>
         </is>
       </c>
     </row>
@@ -30989,7 +30989,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7i49man.pdf printed pp5 and 12; docs/grounding_shielding_plan.md</t>
+          <t xml:space="preserve">7i49man.pdf printed pp5 and 9; docs/grounding_shielding_plan.md</t>
         </is>
       </c>
     </row>
@@ -31493,7 +31493,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mitsubishi M2 Maintenance Manual Fig 14.4-1 printed p250; Z chassis bond not measured</t>
+          <t xml:space="preserve">41434WB p128 dwg 4143075404; Mitsubishi M2 Maintenance Manual Fig 14.4-1 printed p250; Z chassis bond not measured</t>
         </is>
       </c>
     </row>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7i49man.pdf printed pp6 and 12; docs/grounding_shielding_plan.md</t>
+          <t xml:space="preserve">7i49man.pdf printed pp6 and 9; docs/grounding_shielding_plan.md</t>
         </is>
       </c>
     </row>
@@ -32029,7 +32029,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spindle load high</t>
+          <t xml:space="preserve">Spindle load meter (TB2 -LM10)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -32101,7 +32101,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spindle load low</t>
+          <t xml:space="preserve">Spindle load meter common (TB2 -OM)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -32173,7 +32173,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z-axis load high</t>
+          <t xml:space="preserve">Z-axis load meter (ZP6 ZLM wire 37)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -32245,7 +32245,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z-axis load low</t>
+          <t xml:space="preserve">Z-axis load meter common (ZP6 ZOM wire 38)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -51184,7 +51184,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E20"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -51253,7 +51253,7 @@
     <row r="3">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN2-4</t>
+          <t xml:space="preserve">CN2-5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -51273,14 +51273,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magazine position 1 planned as BCD bit 0; confirm bit order at pot</t>
+          <t xml:space="preserve">Magazine position 1 planned as BCD bit 0 (block de-shifted 2026-09-02 per sec 7.5); confirm bit order at pot</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN2-5</t>
+          <t xml:space="preserve">CN2-6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -51307,7 +51307,7 @@
     <row r="5">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN2-6</t>
+          <t xml:space="preserve">CN2-7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -51334,7 +51334,7 @@
     <row r="6">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN2-7</t>
+          <t xml:space="preserve">CN2-8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -51361,7 +51361,7 @@
     <row r="7">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN2-8</t>
+          <t xml:space="preserve">CN2-9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -51381,14 +51381,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magazine position 10 notation planned as fifth BCD bit; confirm identity and bit order</t>
+          <t xml:space="preserve">Magazine position 10 planned as fifth BCD bit; confirm identity and bit order</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN2-9</t>
+          <t xml:space="preserve">CN2-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -51408,19 +51408,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magazine position-OK name match; prove continuity and polarity</t>
+          <t xml:space="preserve">MAGAZINE INPOSITION (MIPRS PRS-13) wire 213; prove continuity and polarity</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN2-14</t>
+          <t xml:space="preserve">CN2-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z_LIMIT_PLUS</t>
+          <t xml:space="preserve">X_HOME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -51435,19 +51435,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">+LTZ / Z positive overtravel name match; retain hardware overtravel path</t>
+          <t xml:space="preserve">*DECX / X-axis zero-return name match; prove continuity and normal state</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN2-15</t>
+          <t xml:space="preserve">CN2-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">X_HOME</t>
+          <t xml:space="preserve">Y_HOME</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -51462,19 +51462,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">*DECX / X-axis zero-return name match; prove continuity and normal state</t>
+          <t xml:space="preserve">*DECY / Y-axis zero-return name match; prove continuity and normal state</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN2-16</t>
+          <t xml:space="preserve">CN3-37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y_HOME</t>
+          <t xml:space="preserve">Y_LIMIT_PLUS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -51489,19 +51489,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">*DECY / Y-axis zero-return name match; prove continuity and normal state</t>
+          <t xml:space="preserve">+LY / Y positive overtravel name match; retain hardware overtravel path</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN3-37</t>
+          <t xml:space="preserve">CN3-38</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y_LIMIT_PLUS</t>
+          <t xml:space="preserve">Z_LIMIT_MINUS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -51516,19 +51516,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">+LY / Y positive overtravel name match; retain hardware overtravel path</t>
+          <t xml:space="preserve">-LZ / Z negative overtravel name match; retain hardware overtravel path</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN3-38</t>
+          <t xml:space="preserve">CN3-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z_LIMIT_MINUS</t>
+          <t xml:space="preserve">SPINDLE_ORIENT_CMD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -51543,19 +51543,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-LZ / Z negative overtravel name match; retain hardware overtravel path</t>
+          <t xml:space="preserve">ORC1 name match; CON1-25 -&gt; T.U. CN3-14 -&gt; (internally) CN4-12 per LOCATED 2026-08-08 dwg 4143075408 p134; previously excluded as ambiguous spindle conductor -- promoted 2026-08-18 on the dwg 4143075403 p127 CON1 pinout reconciliation</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN3-14</t>
+          <t xml:space="preserve">CN3-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE_ORIENT_CMD</t>
+          <t xml:space="preserve">SPINDLE_ORIENT_LOGEAR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -51570,19 +51570,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORC1 name match; CON1-25 -&gt; T.U. CN3-14 -&gt; (internally) CN4-12 per LOCATED 2026-08-08 dwg 4143075408 p134; previously excluded as ambiguous spindle conductor -- promoted 2026-08-18 on the dwg 4143075403 p127 CON1 pinout reconciliation</t>
+          <t xml:space="preserve">CTL name match; CON1-27 -&gt; T.U. CN3-15 -&gt; (internally) CN4-13 per LOCATED 2026-08-08 dwg 4143075408 p134; previously excluded as ambiguous spindle conductor -- promoted 2026-08-18 on the dwg 4143075403 p127 CON1 pinout reconciliation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN3-15</t>
+          <t xml:space="preserve">CN4-1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE_ORIENT_LOGEAR</t>
+          <t xml:space="preserve">SPINDLE_ZERO_SPEED</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -51597,19 +51597,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CTL name match; CON1-27 -&gt; T.U. CN3-15 -&gt; (internally) CN4-13 per LOCATED 2026-08-08 dwg 4143075408 p134; previously excluded as ambiguous spindle conductor -- promoted 2026-08-18 on the dwg 4143075403 p127 CON1 pinout reconciliation</t>
+          <t xml:space="preserve">Spindle zero-speed name match; verify FR-SX contact voltage and polarity</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN4-1</t>
+          <t xml:space="preserve">CN4-3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE_ZERO_SPEED</t>
+          <t xml:space="preserve">SPINDLE_FAULT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -51624,19 +51624,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spindle zero-speed name match; verify FR-SX contact voltage and polarity</t>
+          <t xml:space="preserve">FA/FC name match; CON1-11/-12 -&gt; CN4-3/-4 per RECON 2026-08-08 §D</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN4-3</t>
+          <t xml:space="preserve">CN4-9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE_FAULT</t>
+          <t xml:space="preserve">SPINDLE_FWD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -51651,19 +51651,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">FA/FC name match; CON1-11/-12 -&gt; CN4-3/-4 per RECON 2026-08-08 §D</t>
+          <t xml:space="preserve">SRN name match; CON1-45 -&gt; CN4-9 per RECON 2026-08-08 §D</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN4-9</t>
+          <t xml:space="preserve">CN4-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE_FWD</t>
+          <t xml:space="preserve">SPINDLE_REV</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -51678,19 +51678,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRN name match; CON1-45 -&gt; CN4-9 per RECON 2026-08-08 §D</t>
+          <t xml:space="preserve">SRI name match; CON1-46 -&gt; CN4-10 per RECON 2026-08-08 §D</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN4-10</t>
+          <t xml:space="preserve">CN4-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE_REV</t>
+          <t xml:space="preserve">SPINDLE_ORIENT_ARRIVAL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -51705,19 +51705,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRI name match; CON1-46 -&gt; CN4-10 per RECON 2026-08-08 §D</t>
+          <t xml:space="preserve">ORA1/ORA2 (SETA/SETB were misreads - sec 7.5); CON1-22/-23 -&gt; CN4-16/-17 per RECON 2026-08-08 §D</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CN4-16</t>
+          <t xml:space="preserve">CN6-7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE_ORIENT_ARRIVAL</t>
+          <t xml:space="preserve">SERVO_READY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -51732,39 +51732,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBA1/OBA2 (wire tags SETA/SETB) name match; CON1-22/-23 -&gt; CN4-16/-17 per RECON 2026-08-08 §D</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">CN6-7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVO_READY</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MESA_DIRECT_PLANNED</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED_MATCH</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
           <t xml:space="preserve">Servo-ready name match; confirm this is the retained combined ready contact</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E21"/>
+  <autoFilter ref="A1:E20"/>
 </worksheet>
 </file>
 
@@ -54813,7 +54786,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">none none</t>
+          <t xml:space="preserve">TB2 IN24</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -54823,7 +54796,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">door-interlock</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -54833,12 +54806,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACHINE DOOR INTERLOCK</t>
+          <t xml:space="preserve">DOOR_INTERLOCK</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNALLOCATED</t>
+          <t xml:space="preserve">FACTORY_INTERFACE</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -63497,7 +63470,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">none none</t>
+          <t xml:space="preserve">TB2 OUT11</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -63507,7 +63480,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">flood-coolant</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -63517,12 +63490,12 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLOOD COOLANT MOTOR STARTER (p85 reads 736; p140/p78 read 836 - jacket read decides)</t>
+          <t xml:space="preserve">COOLANT_ON</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNALLOCATED</t>
+          <t xml:space="preserve">FACTORY_INTERFACE</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -65629,7 +65602,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t xml:space="preserve">none none</t>
+          <t xml:space="preserve">TB3 IN4</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -65639,7 +65612,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">spindle-oriented</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -65649,12 +65622,12 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPINDLE ORIENT ARRIVAL</t>
+          <t xml:space="preserve">SPINDLE_ORIENT_ARRIVAL</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNALLOCATED</t>
+          <t xml:space="preserve">FACTORY_INTERFACE</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -70054,7 +70027,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spindle load high</t>
+          <t xml:space="preserve">Spindle load meter (TB2 -LM10)</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -70106,7 +70079,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spindle load low</t>
+          <t xml:space="preserve">Spindle load meter common (TB2 -OM)</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -70158,7 +70131,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z-axis load high</t>
+          <t xml:space="preserve">Z-axis load meter (ZP6 ZLM wire 37)</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -70210,7 +70183,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z-axis load low</t>
+          <t xml:space="preserve">Z-axis load meter common (ZP6 ZOM wire 38)</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -70573,7 +70546,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -70637,7 +70610,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -70733,7 +70706,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">

--- a/wiring/MESAC_Wiring_Crosswalk.xlsx
+++ b/wiring/MESAC_Wiring_Crosswalk.xlsx
@@ -2366,7 +2366,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-23</t>
+          <t xml:space="preserve">1-23</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-40</t>
+          <t xml:space="preserve">1-10</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-20</t>
+          <t xml:space="preserve">1-20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-21</t>
+          <t xml:space="preserve">1-21</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-14</t>
+          <t xml:space="preserve">1-4</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE FWD/REV SW</t>
+          <t xml:space="preserve">MAGAZINE COVER CLOSE (RS-19 MGCCRS X53)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUBE TIMER</t>
+          <t xml:space="preserve">TOOL DETECTOR (PHS-181; p85 CN6-37 reads 391 - jacket read decides)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">lube</t>
+          <t xml:space="preserve">ATC</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-K</t>
+          <t xml:space="preserve">CA4-N</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-12</t>
+          <t xml:space="preserve">CN6-12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-13</t>
+          <t xml:space="preserve">1-16</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-T</t>
+          <t xml:space="preserve">CA4-c</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-U</t>
+          <t xml:space="preserve">CA4-d</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-M</t>
+          <t xml:space="preserve">CA4-r</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-N</t>
+          <t xml:space="preserve">CA4-s</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">0G</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC24V COM (-)</t>
+          <t xml:space="preserve">(not used - blank on source table; 0G is pins 17-18 only per p84/p135)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">common</t>
+          <t xml:space="preserve">spare</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">OEM_POWER_OR_COMMON</t>
+          <t xml:space="preserve">NO_CONNECTION</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t xml:space="preserve">OEM_POWER_OR_COMMON</t>
+          <t xml:space="preserve">NO_CONNECTION</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do not assign to a signal input/output; preserve the documented electrical domain and verify rail disposition separately.</t>
+          <t xml:space="preserve">No conductor to land; positively unused on the cited OEM table.</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNQ-34</t>
+          <t xml:space="preserve">1-41</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-24</t>
+          <t xml:space="preserve">CN6-24</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-</t>
+          <t xml:space="preserve">CA4-g</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOOT SWITCH</t>
+          <t xml:space="preserve">TOOL CLAMP FOOT SWITCH</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-R</t>
+          <t xml:space="preserve">CA4-h</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPARE OUTPUT</t>
+          <t xml:space="preserve">SPARE (INPUT)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-j</t>
+          <t xml:space="preserve">CA4-k</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPARE OUTPUT</t>
+          <t xml:space="preserve">SPARE (OUTPUT)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-k</t>
+          <t xml:space="preserve">CA4-m</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-N</t>
+          <t xml:space="preserve">CA4-n</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-P</t>
+          <t xml:space="preserve">CA4-p</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNQ-29</t>
+          <t xml:space="preserve">1-39</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-14</t>
+          <t xml:space="preserve">1-18</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-34</t>
+          <t xml:space="preserve">4-34 (middle digit low-confidence)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-1</t>
+          <t xml:space="preserve">23-13</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-3</t>
+          <t xml:space="preserve">2-18</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN12-37</t>
+          <t xml:space="preserve">3-2</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN23-9</t>
+          <t xml:space="preserve">2-5</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB1-34</t>
+          <t xml:space="preserve">TB1-*DEC4</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-33</t>
+          <t xml:space="preserve">4-33</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-13</t>
+          <t xml:space="preserve">23-21</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-22</t>
+          <t xml:space="preserve">23-32</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN11-33</t>
+          <t xml:space="preserve">1-33</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN30A TB1-1</t>
+          <t xml:space="preserve">CN301A-17</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-46</t>
+          <t xml:space="preserve">3-46</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIL FUNCTION</t>
+          <t xml:space="preserve">MACHINE MALFUNCTION</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">MFN</t>
+          <t xml:space="preserve">alarm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-20</t>
+          <t xml:space="preserve">3-30</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE TOOL DETECTOR</t>
+          <t xml:space="preserve">MAGAZINE TOOL DETECTOR (p85 reads 391; p84 CN2-13 + p135 read 381 - jacket read decides)</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB23-1</t>
+          <t xml:space="preserve">23-2</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB23-3</t>
+          <t xml:space="preserve">23-3</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB23-4</t>
+          <t xml:space="preserve">23-4</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB23-6</t>
+          <t xml:space="preserve">23-6</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB23-18</t>
+          <t xml:space="preserve">23-18</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-48</t>
+          <t xml:space="preserve">2-18</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOOL CLAMP INTERLOCK</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK (MDINT X1C)</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D2 1-02</t>
+          <t xml:space="preserve">TB5D1-A31</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORI C1</t>
+          <t xml:space="preserve">ORC1</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -16298,12 +16298,12 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROUTE_DEFINED_FIELD_VERIFY</t>
+          <t xml:space="preserve">HOLD_OEM_CONFLICT</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gated by spindle-motion-permit; validate ladder sequence exact drive terminal relay topology and polarity before landing the field wire | [RECON 2026-08-08 §A: element list confirms Y093 ORCM1.M 'SPINDLE ORIENT COMMAND' (.M not .MV) on 060231] | [RECON 2026-08-08 §D: FR-SX CTM] | [LOCATED 2026-08-08: ORC1 CON1-25 wire 4-12 T.U CN3-14, Dwg 4143075408 pg134] | [LADDER-REF 2026-08-10 (approved AG): docs/ladder/spindle_run_ladder_transcription.md]</t>
+          <t xml:space="preserve">Authority wire ORI C1 conflicts with terminal-unit table wire ORC1. Continuity trace required before landing.</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -18190,12 +18190,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-49</t>
+          <t xml:space="preserve">4-49</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D2 2-A3</t>
+          <t xml:space="preserve">WLWT-5</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -18272,12 +18272,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE TIMER</t>
+          <t xml:space="preserve">WAY LUBE WARNING TIMER</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">lube</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-E</t>
+          <t xml:space="preserve">WLWT-14</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -18374,12 +18374,12 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-40</t>
+          <t xml:space="preserve">1-47</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-0122</t>
+          <t xml:space="preserve">TB5D2-b172</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -18466,12 +18466,12 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-38</t>
+          <t xml:space="preserve">1-50</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D2 1-B12</t>
+          <t xml:space="preserve">TB5D2-b182</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1-33</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -23434,12 +23434,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-33</t>
+          <t xml:space="preserve">2-33</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON 2-4</t>
+          <t xml:space="preserve">CON1-4</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -23531,7 +23531,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D2 1-D0</t>
+          <t xml:space="preserve">CON1-50</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -23623,7 +23623,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-12</t>
+          <t xml:space="preserve">CON1-12</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D2 1-A2</t>
+          <t xml:space="preserve">CON1-42</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -23807,7 +23807,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-14</t>
+          <t xml:space="preserve">CON1-14</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -23899,7 +23899,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-7</t>
+          <t xml:space="preserve">CON1-7</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -23991,7 +23991,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-8</t>
+          <t xml:space="preserve">CON1-8</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -24083,7 +24083,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D1 1-A5</t>
+          <t xml:space="preserve">CON1-45</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -24175,7 +24175,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-A-6</t>
+          <t xml:space="preserve">CON1-46</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORI C1</t>
+          <t xml:space="preserve">ORC1</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -24359,7 +24359,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-25</t>
+          <t xml:space="preserve">CON1-25</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -24436,7 +24436,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORIENT LOOP CHECK</t>
+          <t xml:space="preserve">LOW GEAR SHIFT</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -24446,12 +24446,12 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-15</t>
+          <t xml:space="preserve">CN3-15</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-17</t>
+          <t xml:space="preserve">CON1-17</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -24620,7 +24620,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">COM</t>
+          <t xml:space="preserve">COM (p84 reads ORC2; p134 reads COM - annotated ambiguity)</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -24635,7 +24635,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-26</t>
+          <t xml:space="preserve">CON1-26</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -24722,12 +24722,12 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-32</t>
+          <t xml:space="preserve">1-27</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-23</t>
+          <t xml:space="preserve">CON1-22</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -24814,12 +24814,12 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-33</t>
+          <t xml:space="preserve">2-3x (faded)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-24</t>
+          <t xml:space="preserve">CON1-23</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -24906,7 +24906,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5-4</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -24998,7 +24998,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5-5</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -25080,7 +25080,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPEED REFERENCE 3 (10V MAX SPEED)</t>
+          <t xml:space="preserve">SPEED REFERENCE 3 (10V MAX SPEED; p134 mnemonic reads SES)</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -25090,7 +25090,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5-20</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -34830,7 +34830,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNQ-29</t>
+          <t xml:space="preserve">1-39</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -35124,7 +35124,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-14</t>
+          <t xml:space="preserve">1-18</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -35166,7 +35166,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-34</t>
+          <t xml:space="preserve">4-34 (middle digit low-confidence)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -35460,7 +35460,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-23</t>
+          <t xml:space="preserve">1-23</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -35502,7 +35502,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-40</t>
+          <t xml:space="preserve">1-10</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -35670,7 +35670,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-20</t>
+          <t xml:space="preserve">1-20</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -35712,7 +35712,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-21</t>
+          <t xml:space="preserve">1-21</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -35754,7 +35754,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-14</t>
+          <t xml:space="preserve">1-4</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -35828,7 +35828,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE FWD/REV SW</t>
+          <t xml:space="preserve">MAGAZINE COVER CLOSE (RS-19 MGCCRS X53)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -35870,12 +35870,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUBE TIMER</t>
+          <t xml:space="preserve">TOOL DETECTOR (PHS-181; p85 CN6-37 reads 391 - jacket read decides)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">lube</t>
+          <t xml:space="preserve">ATC</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -35885,7 +35885,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-K</t>
+          <t xml:space="preserve">CA4-N</t>
         </is>
       </c>
     </row>
@@ -35922,7 +35922,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-12</t>
+          <t xml:space="preserve">CN6-12</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -35964,12 +35964,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-13</t>
+          <t xml:space="preserve">1-16</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-T</t>
+          <t xml:space="preserve">CA4-c</t>
         </is>
       </c>
     </row>
@@ -36011,7 +36011,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-U</t>
+          <t xml:space="preserve">CA4-d</t>
         </is>
       </c>
     </row>
@@ -36053,7 +36053,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-M</t>
+          <t xml:space="preserve">CA4-r</t>
         </is>
       </c>
     </row>
@@ -36095,7 +36095,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-N</t>
+          <t xml:space="preserve">CA4-s</t>
         </is>
       </c>
     </row>
@@ -36117,17 +36117,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">0G</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC24V COM (-)</t>
+          <t xml:space="preserve">(not used - blank on source table; 0G is pins 17-18 only per p84/p135)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">common</t>
+          <t xml:space="preserve">spare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -36137,7 +36137,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -36216,7 +36216,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNQ-34</t>
+          <t xml:space="preserve">1-41</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-24</t>
+          <t xml:space="preserve">CN6-24</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -36599,7 +36599,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-</t>
+          <t xml:space="preserve">CA4-g</t>
         </is>
       </c>
     </row>
@@ -36626,7 +36626,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOOT SWITCH</t>
+          <t xml:space="preserve">TOOL CLAMP FOOT SWITCH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -36641,7 +36641,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-R</t>
+          <t xml:space="preserve">CA4-h</t>
         </is>
       </c>
     </row>
@@ -36710,7 +36710,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPARE OUTPUT</t>
+          <t xml:space="preserve">SPARE (INPUT)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -36725,7 +36725,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-j</t>
+          <t xml:space="preserve">CA4-k</t>
         </is>
       </c>
     </row>
@@ -36752,7 +36752,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPARE OUTPUT</t>
+          <t xml:space="preserve">SPARE (OUTPUT)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -36767,7 +36767,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-k</t>
+          <t xml:space="preserve">CA4-m</t>
         </is>
       </c>
     </row>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-N</t>
+          <t xml:space="preserve">CA4-n</t>
         </is>
       </c>
     </row>
@@ -36851,7 +36851,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">CA4-P</t>
+          <t xml:space="preserve">CA4-p</t>
         </is>
       </c>
     </row>
@@ -36962,7 +36962,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOOL CLAMP INTERLOCK</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK (MDINT X1C)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -36977,7 +36977,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D2 1-02</t>
+          <t xml:space="preserve">TB5D1-A31</t>
         </is>
       </c>
     </row>
@@ -37251,7 +37251,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORI C1</t>
+          <t xml:space="preserve">ORC1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -37392,12 +37392,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-49</t>
+          <t xml:space="preserve">4-49</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D2 2-A3</t>
+          <t xml:space="preserve">WLWT-5</t>
         </is>
       </c>
     </row>
@@ -37424,12 +37424,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE TIMER</t>
+          <t xml:space="preserve">WAY LUBE WARNING TIMER</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">lube</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -37439,7 +37439,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-E</t>
+          <t xml:space="preserve">WLWT-14</t>
         </is>
       </c>
     </row>
@@ -37476,12 +37476,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-40</t>
+          <t xml:space="preserve">1-47</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-0122</t>
+          <t xml:space="preserve">TB5D2-b172</t>
         </is>
       </c>
     </row>
@@ -37518,12 +37518,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-38</t>
+          <t xml:space="preserve">1-50</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D2 1-B12</t>
+          <t xml:space="preserve">TB5D2-b182</t>
         </is>
       </c>
     </row>
@@ -37812,7 +37812,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1-33</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -37938,12 +37938,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-33</t>
+          <t xml:space="preserve">2-33</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON 2-4</t>
+          <t xml:space="preserve">CON1-4</t>
         </is>
       </c>
     </row>
@@ -37985,7 +37985,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D2 1-D0</t>
+          <t xml:space="preserve">CON1-50</t>
         </is>
       </c>
     </row>
@@ -38027,7 +38027,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-12</t>
+          <t xml:space="preserve">CON1-12</t>
         </is>
       </c>
     </row>
@@ -38069,7 +38069,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D2 1-A2</t>
+          <t xml:space="preserve">CON1-42</t>
         </is>
       </c>
     </row>
@@ -38111,7 +38111,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-14</t>
+          <t xml:space="preserve">CON1-14</t>
         </is>
       </c>
     </row>
@@ -38153,7 +38153,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-7</t>
+          <t xml:space="preserve">CON1-7</t>
         </is>
       </c>
     </row>
@@ -38195,7 +38195,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-8</t>
+          <t xml:space="preserve">CON1-8</t>
         </is>
       </c>
     </row>
@@ -38237,7 +38237,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-D1 1-A5</t>
+          <t xml:space="preserve">CON1-45</t>
         </is>
       </c>
     </row>
@@ -38279,7 +38279,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-A-6</t>
+          <t xml:space="preserve">CON1-46</t>
         </is>
       </c>
     </row>
@@ -38301,7 +38301,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORI C1</t>
+          <t xml:space="preserve">ORC1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -38321,7 +38321,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-25</t>
+          <t xml:space="preserve">CON1-25</t>
         </is>
       </c>
     </row>
@@ -38348,7 +38348,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORIENT LOOP CHECK</t>
+          <t xml:space="preserve">LOW GEAR SHIFT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -38358,12 +38358,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-15</t>
+          <t xml:space="preserve">CN3-15</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-17</t>
+          <t xml:space="preserve">CON1-17</t>
         </is>
       </c>
     </row>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">COM</t>
+          <t xml:space="preserve">COM (p84 reads ORC2; p134 reads COM - annotated ambiguity)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -38405,7 +38405,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-26</t>
+          <t xml:space="preserve">CON1-26</t>
         </is>
       </c>
     </row>
@@ -38442,12 +38442,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-32</t>
+          <t xml:space="preserve">1-27</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-23</t>
+          <t xml:space="preserve">CON1-22</t>
         </is>
       </c>
     </row>
@@ -38484,12 +38484,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-33</t>
+          <t xml:space="preserve">2-3x (faded)</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB5-1-24</t>
+          <t xml:space="preserve">CON1-23</t>
         </is>
       </c>
     </row>
@@ -38568,7 +38568,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-1</t>
+          <t xml:space="preserve">23-13</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -38736,7 +38736,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-3</t>
+          <t xml:space="preserve">2-18</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -38778,7 +38778,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN12-37</t>
+          <t xml:space="preserve">3-2</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -38862,7 +38862,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN23-9</t>
+          <t xml:space="preserve">2-5</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -39077,7 +39077,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB1-34</t>
+          <t xml:space="preserve">TB1-*DEC4</t>
         </is>
       </c>
     </row>
@@ -39324,7 +39324,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-33</t>
+          <t xml:space="preserve">4-33</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -39576,7 +39576,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-13</t>
+          <t xml:space="preserve">23-21</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -39744,7 +39744,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-22</t>
+          <t xml:space="preserve">23-32</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -39870,12 +39870,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN11-33</t>
+          <t xml:space="preserve">1-33</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">CN30A TB1-1</t>
+          <t xml:space="preserve">CN301A-17</t>
         </is>
       </c>
     </row>
@@ -39912,7 +39912,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-46</t>
+          <t xml:space="preserve">3-46</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -39944,12 +39944,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIL FUNCTION</t>
+          <t xml:space="preserve">MACHINE MALFUNCTION</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">MFN</t>
+          <t xml:space="preserve">alarm</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -40332,7 +40332,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-20</t>
+          <t xml:space="preserve">3-30</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -40490,7 +40490,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE TOOL DETECTOR</t>
+          <t xml:space="preserve">MAGAZINE TOOL DETECTOR (p85 reads 391; p84 CN2-13 + p135 read 381 - jacket read decides)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -40584,7 +40584,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB23-1</t>
+          <t xml:space="preserve">23-2</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -40626,7 +40626,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB23-3</t>
+          <t xml:space="preserve">23-3</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -40668,7 +40668,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB23-4</t>
+          <t xml:space="preserve">23-4</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -40710,7 +40710,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB23-6</t>
+          <t xml:space="preserve">23-6</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -40752,7 +40752,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB23-18</t>
+          <t xml:space="preserve">23-18</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -40794,7 +40794,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNB-48</t>
+          <t xml:space="preserve">2-18</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -41693,7 +41693,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -41735,7 +41735,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -41777,7 +41777,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -41819,7 +41819,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -41861,7 +41861,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -41903,7 +41903,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -41945,7 +41945,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -41987,7 +41987,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -42029,7 +42029,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -42071,7 +42071,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -42113,7 +42113,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -42155,7 +42155,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -42197,7 +42197,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -42239,7 +42239,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -42281,7 +42281,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -42323,7 +42323,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -42365,7 +42365,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -42407,7 +42407,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -42449,7 +42449,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -42491,7 +42491,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -42533,7 +42533,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -42575,7 +42575,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -42617,7 +42617,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -42659,7 +42659,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -42701,7 +42701,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -42743,7 +42743,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -42785,7 +42785,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -42827,7 +42827,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -42869,7 +42869,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -42953,7 +42953,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -42995,7 +42995,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -43037,7 +43037,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -43121,7 +43121,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -43163,7 +43163,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -43205,7 +43205,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -43247,7 +43247,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -43289,7 +43289,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -43331,7 +43331,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR-20 (AMD/LFH)</t>
+          <t xml:space="preserve">MR-20 (RMD/LFH)</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -49656,7 +49656,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5-4</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -49698,7 +49698,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5-5</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -49730,7 +49730,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPEED REFERENCE 3 (10V MAX SPEED)</t>
+          <t xml:space="preserve">SPEED REFERENCE 3 (10V MAX SPEED; p134 mnemonic reads SES)</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -49740,7 +49740,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5-20</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -53439,7 +53439,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE FWD/REV SW</t>
+          <t xml:space="preserve">MAGAZINE COVER CLOSE (RS-19 MGCCRS X53)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -53491,7 +53491,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUBE TIMER</t>
+          <t xml:space="preserve">TOOL DETECTOR (PHS-181; p85 CN6-37 reads 391 - jacket read decides)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -53516,7 +53516,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">lube</t>
+          <t xml:space="preserve">ATC</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -53803,7 +53803,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC24V COM (-)</t>
+          <t xml:space="preserve">(not used - blank on source table; 0G is pins 17-18 only per p84/p135)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -53813,12 +53813,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">0G</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC24V COM (-)</t>
+          <t xml:space="preserve">(not used - blank on source table; 0G is pins 17-18 only per p84/p135)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -53828,7 +53828,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">common</t>
+          <t xml:space="preserve">spare</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -55103,7 +55103,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOOT SWITCH</t>
+          <t xml:space="preserve">TOOL CLAMP FOOT SWITCH</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -55207,7 +55207,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPARE OUTPUT</t>
+          <t xml:space="preserve">SPARE (INPUT)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -55222,7 +55222,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPARE OUTPUT</t>
+          <t xml:space="preserve">SPARE (INPUT)</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -55259,7 +55259,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPARE OUTPUT</t>
+          <t xml:space="preserve">SPARE (OUTPUT)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -55274,7 +55274,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPARE OUTPUT</t>
+          <t xml:space="preserve">SPARE (OUTPUT)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -58483,7 +58483,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIL FUNCTION</t>
+          <t xml:space="preserve">MACHINE MALFUNCTION</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -58498,7 +58498,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIL FUNCTION</t>
+          <t xml:space="preserve">MACHINE MALFUNCTION</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -58508,7 +58508,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">MFN</t>
+          <t xml:space="preserve">alarm</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -59419,7 +59419,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE TOOL DETECTOR</t>
+          <t xml:space="preserve">MAGAZINE TOOL DETECTOR (p85 reads 391; p84 CN2-13 + p135 read 381 - jacket read decides)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -59434,7 +59434,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE TOOL DETECTOR</t>
+          <t xml:space="preserve">MAGAZINE TOOL DETECTOR (p85 reads 391; p84 CN2-13 + p135 read 381 - jacket read decides)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -60251,7 +60251,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOOL CLAMP INTERLOCK</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK (MDINT X1C)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -60266,7 +60266,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOOL CLAMP INTERLOCK</t>
+          <t xml:space="preserve">MACHINE DOOR INTERLOCK (MDINT X1C)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -60833,7 +60833,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORI C1</t>
+          <t xml:space="preserve">ORC1</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -61967,7 +61967,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE TIMER</t>
+          <t xml:space="preserve">WAY LUBE WARNING TIMER</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -61982,7 +61982,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE TIMER</t>
+          <t xml:space="preserve">WAY LUBE WARNING TIMER</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -61992,7 +61992,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATC</t>
+          <t xml:space="preserve">lube</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -65409,7 +65409,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORI C1</t>
+          <t xml:space="preserve">ORC1</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -65451,7 +65451,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORIENT LOOP CHECK</t>
+          <t xml:space="preserve">LOW GEAR SHIFT</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -65466,7 +65466,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORIENT LOOP CHECK</t>
+          <t xml:space="preserve">LOW GEAR SHIFT</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -65555,22 +65555,22 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
+          <t xml:space="preserve">COM (p84 reads ORC2; p134 reads COM - annotated ambiguity)</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
           <t xml:space="preserve">COM</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">none</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COM</t>
-        </is>
-      </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">COM</t>
+          <t xml:space="preserve">COM (p84 reads ORC2; p134 reads COM - annotated ambiguity)</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -65815,7 +65815,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPEED REFERENCE 3 (10V MAX SPEED)</t>
+          <t xml:space="preserve">SPEED REFERENCE 3 (10V MAX SPEED; p134 mnemonic reads SES)</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
